--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -461,7 +461,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>last_updated_utc</t>
+          <t>last_updated_ist</t>
         </is>
       </c>
     </row>
@@ -617,11 +617,7 @@
           <t>https://www.moneycontrol.com/ipo/renewables/junipergreenenergy/JGE</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2026-08-07 11:09:00</t>
-        </is>
-      </c>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -687,11 +683,7 @@
           <t>https://www.moneycontrol.com/ipo/electric-equipment-switchgears/mvelectrosystems/MEL04</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2026-08-07 11:09:00</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -755,7 +747,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-08-07 11:17:22</t>
+          <t>2026-08-07 16:49:33</t>
         </is>
       </c>
     </row>
@@ -821,7 +813,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-08-07 11:17:22</t>
+          <t>2026-08-07 16:49:33</t>
         </is>
       </c>
     </row>
@@ -887,7 +879,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-08-07 11:17:22</t>
+          <t>2026-08-07 16:49:33</t>
         </is>
       </c>
     </row>
@@ -949,7 +941,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-08-07 11:17:22</t>
+          <t>2026-08-07 16:49:33</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1003,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-08-07 11:17:22</t>
+          <t>2026-08-07 16:49:33</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1065,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-08-07 11:17:22</t>
+          <t>2026-08-07 16:49:33</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1127,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-08-07 11:17:22</t>
+          <t>2026-08-07 16:49:33</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1189,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-08-07 11:17:22</t>
+          <t>2026-08-07 16:49:33</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -747,7 +747,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-08-07 16:49:33</t>
+          <t>2026-08-07 21:39:23</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-08-07 16:49:33</t>
+          <t>2026-08-07 21:39:23</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-08-07 16:49:33</t>
+          <t>2026-08-07 21:39:23</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-08-07 16:49:33</t>
+          <t>2026-08-07 21:39:23</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-08-07 16:49:33</t>
+          <t>2026-08-07 21:39:23</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-08-07 16:49:33</t>
+          <t>2026-08-07 21:39:23</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-08-07 16:49:33</t>
+          <t>2026-08-07 21:39:23</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-08-07 16:49:33</t>
+          <t>2026-08-07 21:39:23</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$P$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$P$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -688,7 +688,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ardee Industries</t>
+          <t>LEAP India Ltd</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -698,63 +698,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aug 05, 2026</t>
+          <t>Aug 07, 2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Aug 07, 2026</t>
+          <t>Aug 11, 2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aug 10, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>159</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>14946</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/ardeeindustries/AIL11</t>
+          <t>https://www.moneycontrol.com/ipo/leapindialtd/LIL07</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-08-07 21:39:23</t>
+          <t>2026-08-08 09:58:36</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LEAP India Ltd</t>
+          <t>Technocraft Ventures Ltd</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -784,109 +784,105 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>212</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/leapindialtd/LIL07</t>
+          <t>https://www.moneycontrol.com/ipo/technocraftventuresltd/TVL</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-08-07 21:39:23</t>
+          <t>2026-08-08 09:58:36</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Technocraft Ventures Ltd</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>Dhoot Transmission Ltd</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aug 07, 2026</t>
+          <t>Aug 10, 2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Aug 11, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>829-871</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14840</t>
+          <t>14807</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocraftventuresltd/TVL</t>
+          <t>https://www.moneycontrol.com/ipo/dhoottransmissionltd/DTL02</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-08-07 21:39:23</t>
+          <t>2026-08-08 09:58:36</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dhoot Transmission Ltd</t>
+          <t>Molbio Diagnostics Ltd</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -916,17 +912,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>829-871</t>
+          <t>768-807</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14807</t>
+          <t>14526</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -936,19 +932,19 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/dhoottransmissionltd/DTL02</t>
+          <t>https://www.moneycontrol.com/ipo/molbiodiagnosticsltd/MDL02</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-08-07 21:39:23</t>
+          <t>2026-08-08 09:58:36</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics Ltd</t>
+          <t>Milky Mist Dairy Food Ltd</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -958,37 +954,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aug 10, 2026</t>
+          <t>Aug 11, 2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>768-807</t>
+          <t>133-140</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14526</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -998,19 +994,19 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/molbiodiagnosticsltd/MDL02</t>
+          <t>https://www.moneycontrol.com/ipo/milkymistdairyfoodltd/MMD</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-08-07 21:39:23</t>
+          <t>2026-08-08 09:58:36</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food Ltd</t>
+          <t>Behari Lal Engineering Ltd</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1020,37 +1016,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aug 11, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>133-140</t>
+          <t>271-285</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>14980</t>
+          <t>14820</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1060,19 +1056,19 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/milkymistdairyfoodltd/MMD</t>
+          <t>https://www.moneycontrol.com/ipo/beharilalengineeringltd/BLE</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-08-07 21:39:23</t>
+          <t>2026-08-08 09:58:36</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering Ltd</t>
+          <t>Shiprocket Ltd</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1102,17 +1098,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>271-285</t>
+          <t>92-97</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>14820</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1122,79 +1118,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/beharilalengineeringltd/BLE</t>
+          <t>https://www.moneycontrol.com/ipo/shiprocketltd/SL26</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-08-07 21:39:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Shiprocket Ltd</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Aug 12, 2026</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Aug 14, 2026</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Aug 17, 2026</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Aug 19, 2026</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>92-97</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>14938</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>https://www.moneycontrol.com/ipo/shiprocketltd/SL26</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2026-08-07 21:39:23</t>
+          <t>2026-08-08 09:58:36</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P11"/>
+  <autoFilter ref="A1:P10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -747,7 +747,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-08-08 09:58:36</t>
+          <t>2026-08-08 21:16:31</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-08-08 09:58:36</t>
+          <t>2026-08-08 21:16:31</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-08-08 09:58:36</t>
+          <t>2026-08-08 21:16:31</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-08-08 09:58:36</t>
+          <t>2026-08-08 21:16:31</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-08-08 09:58:36</t>
+          <t>2026-08-08 21:16:31</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-08-08 09:58:36</t>
+          <t>2026-08-08 21:16:31</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-08-08 09:58:36</t>
+          <t>2026-08-08 21:16:31</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$P$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$P$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,7 +32,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBBF7D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5E7EB"/>
       </patternFill>
     </fill>
     <fill>
@@ -72,12 +77,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -688,303 +694,295 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LEAP India Ltd</t>
+          <t>Anawil Wire &amp; Engineering</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Aug 07, 2026</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Aug 11, 2026</t>
-        </is>
-      </c>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 06, 2025</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 10, 2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>270</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>108000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>139</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/leapindialtd/LIL07</t>
+          <t>https://www.moneycontrol.com/ipo/anawilwireengineering/AWEL</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-08-08 21:16:31</t>
+          <t>2026-08-09 10:07:10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Technocraft Ventures Ltd</t>
+          <t>Ardee Industries</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Aug 07, 2026</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Aug 11, 2026</t>
-        </is>
-      </c>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Aug 10, 2026</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Aug 12, 2026</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Aug 14, 2026</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>281</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14840</t>
+          <t>14893</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocraftventuresltd/TVL</t>
+          <t>https://www.moneycontrol.com/ipo/ardeeindustries/AIL11</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-08-08 21:16:31</t>
+          <t>2026-08-09 10:07:10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dhoot Transmission Ltd</t>
+          <t>LEAP India Ltd</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aug 10, 2026</t>
+          <t>Aug 07, 2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Aug 11, 2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Aug 12, 2026</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Aug 13, 2026</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>829-871</t>
+          <t>159</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14807</t>
+          <t>14946</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/dhoottransmissionltd/DTL02</t>
+          <t>https://www.moneycontrol.com/ipo/leapindialtd/LIL07</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-08-08 21:16:31</t>
+          <t>2026-08-09 10:07:10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics Ltd</t>
+          <t>Technocraft Ventures Ltd</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aug 10, 2026</t>
+          <t>Aug 07, 2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Aug 11, 2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Aug 12, 2026</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Aug 13, 2026</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>768-807</t>
+          <t>212</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14526</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/molbiodiagnosticsltd/MDL02</t>
+          <t>https://www.moneycontrol.com/ipo/technocraftventuresltd/TVL</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-08-08 21:16:31</t>
+          <t>2026-08-09 10:07:10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food Ltd</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+          <t>Dhoot Transmission Ltd</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aug 11, 2026</t>
+          <t>Aug 10, 2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Aug 13, 2026</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Aug 14, 2026</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>133-140</t>
+          <t>829-871</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14980</t>
+          <t>14807</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -994,59 +992,59 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/milkymistdairyfoodltd/MMD</t>
+          <t>https://www.moneycontrol.com/ipo/dhoottransmissionltd/DTL02</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-08-08 21:16:31</t>
+          <t>2026-08-09 10:07:10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering Ltd</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+          <t>Molbio Diagnostics Ltd</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Aug 10, 2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>Aug 12, 2026</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Aug 14, 2026</t>
-        </is>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Aug 13, 2026</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Aug 17, 2026</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Aug 19, 2026</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>271-285</t>
+          <t>768-807</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>14820</t>
+          <t>14526</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1056,59 +1054,59 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/beharilalengineeringltd/BLE</t>
+          <t>https://www.moneycontrol.com/ipo/molbiodiagnosticsltd/MDL02</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-08-08 21:16:31</t>
+          <t>2026-08-09 10:07:10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shiprocket Ltd</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+          <t>Milky Mist Dairy Food Ltd</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 11, 2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Aug 13, 2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Aug 14, 2026</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Aug 17, 2026</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>92-97</t>
+          <t>133-140</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>14938</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1118,17 +1116,191 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/milkymistdairyfoodltd/MMD</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:07:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Behari Lal Engineering Ltd</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aug 17, 2026</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>271-285</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>14820</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/beharilalengineeringltd/BLE</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:07:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Shiprocket Ltd</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aug 17, 2026</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>92-97</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>14938</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/shiprocketltd/SL26</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2026-08-08 21:16:31</t>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:07:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Q&amp;T Foods Ltd</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aug 17, 2026</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:07:10</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P10"/>
+  <autoFilter ref="A1:P13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -745,7 +745,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-08-09 10:07:10</t>
+          <t>2026-08-09 21:17:10</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-08-09 10:07:10</t>
+          <t>2026-08-09 21:17:10</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-08-09 10:07:10</t>
+          <t>2026-08-09 21:17:10</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-08-09 10:07:10</t>
+          <t>2026-08-09 21:17:10</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-08-09 10:07:10</t>
+          <t>2026-08-09 21:17:10</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-08-09 10:07:10</t>
+          <t>2026-08-09 21:17:10</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-08-09 10:07:10</t>
+          <t>2026-08-09 21:17:10</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-08-09 10:07:10</t>
+          <t>2026-08-09 21:17:10</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-08-09 10:07:10</t>
+          <t>2026-08-09 21:17:10</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-08-09 10:07:10</t>
+          <t>2026-08-09 21:17:10</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -697,9 +697,9 @@
           <t>Anawil Wire &amp; Engineering</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -740,12 +740,12 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/anawilwireengineering/AWEL</t>
+          <t>https://www.moneycontrol.com/ipo/infrastructure/anawilwireengineering/AWEL</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-08-09 21:17:10</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-08-09 21:17:10</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-08-09 21:17:10</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-08-09 21:17:10</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
@@ -945,9 +945,9 @@
           <t>Dhoot Transmission Ltd</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>829-871</t>
+          <t>871</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-08-09 21:17:10</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
@@ -1007,9 +1007,9 @@
           <t>Molbio Diagnostics Ltd</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>768-807</t>
+          <t>807</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-08-09 21:17:10</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-08-09 21:17:10</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-08-09 21:17:10</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-08-09 21:17:10</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-08-09 21:17:10</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$P$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$P$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -803,7 +803,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-10 21:39:34</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-10 21:39:34</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -935,7 +935,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-10 21:39:34</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,11 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -997,7 +1001,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-10 21:39:34</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1053,11 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -1059,7 +1067,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-10 21:39:34</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1129,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-10 21:39:34</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1191,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-10 21:39:34</t>
         </is>
       </c>
     </row>
@@ -1245,14 +1253,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-10 21:39:34</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1262,24 +1270,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1290,17 +1298,75 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Q&amp;T Foods Ltd</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aug 17, 2026</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P13"/>
+  <autoFilter ref="A1:P14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -803,7 +803,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-08-10 21:39:34</t>
+          <t>2026-08-10 22:20:27</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-08-10 21:39:34</t>
+          <t>2026-08-10 22:20:27</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-08-10 21:39:34</t>
+          <t>2026-08-10 22:20:27</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-08-10 21:39:34</t>
+          <t>2026-08-10 22:20:27</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-08-10 21:39:34</t>
+          <t>2026-08-10 22:20:27</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-08-10 21:39:34</t>
+          <t>2026-08-10 22:20:27</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-08-10 21:39:34</t>
+          <t>2026-08-10 22:20:27</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-08-10 21:39:34</t>
+          <t>2026-08-10 22:20:27</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-08-10 21:39:34</t>
+          <t>2026-08-10 22:20:27</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -483,77 +483,82 @@
           <t>company_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>got_ipo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ipo_status</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>open_date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>close_date</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>allotment_date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>listing_date</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>lot_size</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>price_band</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>invested</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>listing_price</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>output</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>total_subsc</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>listing_gain</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>listing_gain%</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>last_updated_ist</t>
         </is>
@@ -565,65 +570,61 @@
           <t>Juniper Green Energy</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Listed</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Aug 06, 2026</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>225</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>14850</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>245</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>16170</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>1320</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/renewables/junipergreenenergy/JGE</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -631,65 +632,61 @@
           <t>MV Electrosystems</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Listed</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Aug 06, 2026</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>425</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>14450</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>520</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>17680</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>189</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>3230</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/electric-equipment-switchgears/mvelectrosystems/MEL04</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -697,53 +694,47 @@
           <t>Anawil Wire &amp; Engineering</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Listed</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Aug 06, 2025</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Aug 10, 2026</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>270</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>108000</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>139</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/infrastructure/anawilwireengineering/AWEL</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>2026-08-10 10:24:29</t>
         </is>
@@ -755,53 +746,47 @@
           <t>Ardee Industries</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Aug 10, 2026</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Aug 12, 2026</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>14893</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/ardeeindustries/AIL11</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>2026-08-10 21:39:34</t>
         </is>
@@ -813,61 +798,62 @@
           <t>LEAP India Ltd</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Aug 07, 2026</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Aug 11, 2026</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Aug 12, 2026</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Aug 14, 2026</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>159</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>14946</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/leapindialtd/LIL07</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2026-08-10 21:39:34</t>
         </is>
@@ -879,61 +865,57 @@
           <t>Technocraft Ventures Ltd</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Aug 07, 2026</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Aug 11, 2026</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Aug 12, 2026</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Aug 14, 2026</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>212</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>14840</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/technocraftventuresltd/TVL</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>2026-08-10 21:39:34</t>
         </is>
@@ -945,61 +927,57 @@
           <t>Dhoot Transmission Ltd</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Aug 10, 2026</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Aug 12, 2026</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Aug 13, 2026</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Aug 17, 2026</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>871</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>14807</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/dhoottransmissionltd/DTL02</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>2026-08-10 21:39:34</t>
         </is>
@@ -1011,61 +989,57 @@
           <t>Molbio Diagnostics Ltd</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Aug 10, 2026</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Aug 12, 2026</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Aug 13, 2026</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Aug 17, 2026</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>807</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>14526</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/molbiodiagnosticsltd/MDL02</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>2026-08-10 21:39:34</t>
         </is>
@@ -1077,57 +1051,52 @@
           <t>Milky Mist Dairy Food Ltd</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Aug 11, 2026</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Aug 13, 2026</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Aug 14, 2026</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Aug 18, 2026</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>133-140</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>14980</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/milkymistdairyfoodltd/MMD</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>2026-08-10 21:39:34</t>
         </is>
@@ -1139,57 +1108,52 @@
           <t>Behari Lal Engineering Ltd</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Aug 12, 2026</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Aug 14, 2026</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Aug 17, 2026</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Aug 19, 2026</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>271-285</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>14820</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/beharilalengineeringltd/BLE</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>2026-08-10 21:39:34</t>
         </is>
@@ -1201,57 +1165,52 @@
           <t>Shiprocket Ltd</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Aug 12, 2026</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Aug 14, 2026</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Aug 17, 2026</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Aug 19, 2026</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>92-97</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>14938</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/shiprocketltd/SL26</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>2026-08-10 21:39:34</t>
         </is>
@@ -1263,45 +1222,37 @@
           <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Aug 13, 2026</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Aug 17, 2026</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Aug 18, 2026</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>179-189</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>2026-08-10 21:39:34</t>
         </is>
@@ -1313,53 +1264,47 @@
           <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Aug 12, 2026</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Aug 14, 2026</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Aug 17, 2026</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>138000</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>2026-08-10 10:24:29</t>
         </is>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-08-10 22:28:45</t>
+          <t>2026-08-10 22:29:10</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-08-10 22:28:45</t>
+          <t>2026-08-10 22:29:10</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-08-10 22:28:45</t>
+          <t>2026-08-10 22:29:10</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-08-10 22:28:45</t>
+          <t>2026-08-10 22:29:10</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-08-10 22:28:45</t>
+          <t>2026-08-10 22:29:10</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-08-10 22:28:45</t>
+          <t>2026-08-10 22:29:10</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-08-10 22:28:45</t>
+          <t>2026-08-10 22:29:10</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-10 22:28:45</t>
+          <t>2026-08-10 22:29:10</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-08-10 22:28:45</t>
+          <t>2026-08-10 22:29:10</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-08-10 22:29:10</t>
+          <t>2026-08-10 22:40:53</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-08-10 22:29:10</t>
+          <t>2026-08-10 22:40:53</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-08-10 22:29:10</t>
+          <t>2026-08-10 22:40:53</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-08-10 22:29:10</t>
+          <t>2026-08-10 22:40:53</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-08-10 22:29:10</t>
+          <t>2026-08-10 22:40:53</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-08-10 22:29:10</t>
+          <t>2026-08-10 22:40:53</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-08-10 22:29:10</t>
+          <t>2026-08-10 22:40:53</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-10 22:29:10</t>
+          <t>2026-08-10 22:40:53</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-08-10 22:29:10</t>
+          <t>2026-08-10 22:40:53</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-08-10 22:40:53</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-08-10 22:40:53</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-08-10 22:40:53</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-08-10 22:40:53</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-08-10 22:40:53</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-08-10 22:40:53</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-08-10 22:40:53</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-10 22:40:53</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-08-10 22:40:53</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-11 10:10:14</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-11 10:10:14</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -950,7 +950,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-11 10:10:14</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-11 10:10:14</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-11 10:10:14</t>
         </is>
       </c>
     </row>
@@ -1095,9 +1095,9 @@
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>133-140</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-11 10:10:14</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-11 10:10:14</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-11 10:10:14</t>
         </is>
       </c>
     </row>
@@ -1305,13 +1305,21 @@
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>179-189</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>113400</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-08-11 10:10:14</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-08-11 10:10:14</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -950,7 +950,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-08-11 10:10:14</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-08-11 10:10:14</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-08-11 10:10:14</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,11 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1147,7 +1151,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-08-11 10:10:14</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1214,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-08-11 10:10:14</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
@@ -1273,14 +1277,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-11 10:10:14</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Lalithaa Jewellery Mart Ltd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1291,33 +1295,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Aug 20, 2026</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Aug 24, 2026</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>190-201</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>14874</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1327,19 +1335,19 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/lalithaajewellerymartltd/LJML</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Shankesh Jewellers Ltd</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1350,33 +1358,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 20, 2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Aug 21, 2026</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>88-93</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1386,17 +1398,249 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/shankeshjewellersltd/SJL01</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2026-08-11 21:41:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sunshine Pictures Ltd</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aug 20, 2026</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Aug 21, 2026</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>342-360</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>14760</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/sunshinepicturesltd/SPL13</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2026-08-11 21:41:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Credent Connect N Care Ltd</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Aug 13, 2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aug 17, 2026</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>179-189</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>113400</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:43:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Q&amp;T Foods Ltd</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Aug 17, 2026</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2026-08-11 21:41:02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q14"/>
+  <autoFilter ref="A1:Q18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -764,9 +764,9 @@
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -807,12 +807,12 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/ardeeindustries/AIL11</t>
+          <t>https://www.moneycontrol.com/ipo/metals-non-ferrous/ardeeindustries/AIL11</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-12 10:33:00</t>
         </is>
       </c>
     </row>
@@ -827,9 +827,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -871,7 +871,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-12 10:33:00</t>
         </is>
       </c>
     </row>
@@ -894,9 +894,9 @@
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>39</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -950,7 +950,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-12 10:33:00</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-12 10:33:00</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-12 10:33:00</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-12 10:33:00</t>
         </is>
       </c>
     </row>
@@ -1162,9 +1162,9 @@
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>271-285</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-12 10:33:00</t>
         </is>
       </c>
     </row>
@@ -1225,9 +1225,9 @@
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>92-97</t>
+          <t>97</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-12 10:33:00</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-12 10:33:00</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-12 10:33:00</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-12 10:33:00</t>
         </is>
       </c>
     </row>
@@ -1616,13 +1616,21 @@
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>125-132</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -570,15 +570,11 @@
           <t>Juniper Green Energy</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Listed</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Aug 06, 2026</t>
@@ -629,7 +625,6 @@
           <t>https://www.moneycontrol.com/ipo/renewables/junipergreenenergy/JGE</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -637,15 +632,11 @@
           <t>MV Electrosystems</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Listed</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Aug 06, 2026</t>
@@ -696,7 +687,6 @@
           <t>https://www.moneycontrol.com/ipo/electric-equipment-switchgears/mvelectrosystems/MEL04</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -704,14 +694,11 @@
           <t>Anawil Wire &amp; Engineering</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Listed</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Aug 06, 2025</t>
@@ -737,15 +724,11 @@
           <t>108000</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>139</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/infrastructure/anawilwireengineering/AWEL</t>
@@ -763,14 +746,11 @@
           <t>Ardee Industries</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Listed</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Aug 10, 2026</t>
@@ -796,15 +776,11 @@
           <t>14893</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/metals-non-ferrous/ardeeindustries/AIL11</t>
@@ -867,15 +843,11 @@
           <t>14946</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/leapindialtd/LIL07</t>
@@ -893,7 +865,6 @@
           <t>Technocraft Ventures Ltd</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
@@ -934,15 +905,11 @@
           <t>14840</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/technocraftventuresltd/TVL</t>
@@ -960,7 +927,6 @@
           <t>Dhoot Transmission Ltd</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Open</t>
@@ -1001,15 +967,11 @@
           <t>14807</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/dhoottransmissionltd/DTL02</t>
@@ -1027,7 +989,6 @@
           <t>Molbio Diagnostics Ltd</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Open</t>
@@ -1068,15 +1029,11 @@
           <t>14526</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/molbiodiagnosticsltd/MDL02</t>
@@ -1094,7 +1051,6 @@
           <t>Milky Mist Dairy Food Ltd</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Open</t>
@@ -1135,15 +1091,11 @@
           <t>14980</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/milkymistdairyfoodltd/MMD</t>
@@ -1161,7 +1113,6 @@
           <t>Behari Lal Engineering Ltd</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Open</t>
@@ -1202,11 +1153,6 @@
           <t>14820</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/beharilalengineeringltd/BLE</t>
@@ -1224,7 +1170,6 @@
           <t>Shiprocket Ltd</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Open</t>
@@ -1265,11 +1210,6 @@
           <t>14938</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/shiprocketltd/SL26</t>
@@ -1287,7 +1227,6 @@
           <t>Lalithaa Jewellery Mart Ltd</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
@@ -1328,11 +1267,6 @@
           <t>14874</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/lalithaajewellerymartltd/LJML</t>
@@ -1350,7 +1284,6 @@
           <t>Shankesh Jewellers Ltd</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
@@ -1391,11 +1324,6 @@
           <t>14880</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/shankeshjewellersltd/SJL01</t>
@@ -1413,7 +1341,6 @@
           <t>Sunshine Pictures Ltd</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
@@ -1454,11 +1381,6 @@
           <t>14760</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/sunshinepicturesltd/SPL13</t>
@@ -1476,7 +1398,6 @@
           <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
@@ -1497,7 +1418,6 @@
           <t>Aug 18, 2026</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>600</t>
@@ -1513,11 +1433,6 @@
           <t>113400</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
@@ -1535,7 +1450,6 @@
           <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
@@ -1556,7 +1470,6 @@
           <t>Aug 17, 2026</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>1200</t>
@@ -1572,11 +1485,6 @@
           <t>138000</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
@@ -1594,7 +1502,6 @@
           <t>Technocrats Plasma Systems Ltd</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
@@ -1615,7 +1522,6 @@
           <t>Aug 19, 2026</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>1000</t>
@@ -1631,11 +1537,6 @@
           <t>132000</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -865,6 +865,11 @@
           <t>Technocraft Ventures Ltd</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Closed</t>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="82">
   <si>
     <t>company_name</t>
   </si>
@@ -67,42 +67,48 @@
     <t>Juniper Green Energy</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Listed</t>
+  </si>
+  <si>
+    <t>Aug 06, 2026</t>
+  </si>
+  <si>
+    <t>https://www.moneycontrol.com/ipo/renewables/junipergreenenergy/JGE</t>
+  </si>
+  <si>
+    <t>MV Electrosystems</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>https://www.moneycontrol.com/ipo/electric-equipment-switchgears/mvelectrosystems/MEL04</t>
+  </si>
+  <si>
+    <t>Anawil Wire &amp; Engineering</t>
+  </si>
+  <si>
+    <t>Aug 06, 2025</t>
+  </si>
+  <si>
+    <t>Aug 10, 2026</t>
+  </si>
+  <si>
+    <t>https://www.moneycontrol.com/ipo/infrastructure/anawilwireengineering/AWEL</t>
+  </si>
+  <si>
+    <t>2026-08-10 10:24:29</t>
+  </si>
+  <si>
+    <t>Ardee Industries</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
-    <t>Listed</t>
-  </si>
-  <si>
-    <t>Aug 06, 2026</t>
-  </si>
-  <si>
-    <t>https://www.moneycontrol.com/ipo/renewables/junipergreenenergy/JGE</t>
-  </si>
-  <si>
-    <t>MV Electrosystems</t>
-  </si>
-  <si>
-    <t>https://www.moneycontrol.com/ipo/electric-equipment-switchgears/mvelectrosystems/MEL04</t>
-  </si>
-  <si>
-    <t>Anawil Wire &amp; Engineering</t>
-  </si>
-  <si>
-    <t>Aug 06, 2025</t>
-  </si>
-  <si>
-    <t>Aug 10, 2026</t>
-  </si>
-  <si>
-    <t>https://www.moneycontrol.com/ipo/infrastructure/anawilwireengineering/AWEL</t>
-  </si>
-  <si>
-    <t>2026-08-10 10:24:29</t>
-  </si>
-  <si>
-    <t>Ardee Industries</t>
-  </si>
-  <si>
     <t>Aug 12, 2026</t>
   </si>
   <si>
@@ -113,9 +119,6 @@
   </si>
   <si>
     <t>LEAP India Ltd</t>
-  </si>
-  <si>
-    <t>Yes</t>
   </si>
   <si>
     <t>Closed</t>
@@ -786,7 +789,7 @@
         <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>19</v>
@@ -819,12 +822,12 @@
         <v>22</v>
       </c>
       <c r="P3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
@@ -833,10 +836,10 @@
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4">
         <v>400</v>
@@ -851,27 +854,27 @@
         <v>139</v>
       </c>
       <c r="P4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H5">
         <v>281</v>
@@ -886,33 +889,33 @@
         <v>134</v>
       </c>
       <c r="P5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6">
         <v>94</v>
@@ -927,33 +930,33 @@
         <v>8</v>
       </c>
       <c r="P6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H7">
         <v>70</v>
@@ -968,30 +971,30 @@
         <v>39</v>
       </c>
       <c r="P7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H8">
         <v>17</v>
@@ -1006,30 +1009,30 @@
         <v>4</v>
       </c>
       <c r="P8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H9">
         <v>18</v>
@@ -1044,30 +1047,30 @@
         <v>3</v>
       </c>
       <c r="P9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H10">
         <v>107</v>
@@ -1082,30 +1085,30 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H11">
         <v>52</v>
@@ -1117,30 +1120,30 @@
         <v>14820</v>
       </c>
       <c r="P11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H12">
         <v>154</v>
@@ -1152,164 +1155,164 @@
         <v>14938</v>
       </c>
       <c r="P12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H13">
         <v>74</v>
       </c>
       <c r="I13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J13">
         <v>14874</v>
       </c>
       <c r="P13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H14">
         <v>160</v>
       </c>
       <c r="I14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J14">
         <v>14880</v>
       </c>
       <c r="P14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H15">
         <v>41</v>
       </c>
       <c r="I15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J15">
         <v>14760</v>
       </c>
       <c r="P15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H16">
         <v>600</v>
       </c>
       <c r="I16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J16">
         <v>113400</v>
       </c>
       <c r="P16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H17">
         <v>1200</v>
@@ -1321,42 +1324,42 @@
         <v>138000</v>
       </c>
       <c r="P17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H18">
         <v>1000</v>
       </c>
       <c r="I18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J18">
         <v>132000</v>
       </c>
       <c r="P18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -885,8 +885,20 @@
       <c r="J5">
         <v>14893</v>
       </c>
+      <c r="K5">
+        <v>72</v>
+      </c>
+      <c r="L5">
+        <v>20232</v>
+      </c>
       <c r="M5">
         <v>134</v>
+      </c>
+      <c r="N5">
+        <v>5339</v>
+      </c>
+      <c r="O5">
+        <v>36</v>
       </c>
       <c r="P5" t="s">
         <v>33</v>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -851,34 +851,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LEAP India Ltd</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Aug 07, 2026</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Aug 11, 2026</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Aug 12, 2026</t>
-        </is>
-      </c>
+          <t>LEAP India</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Aug 14, 2026</t>
@@ -899,35 +883,51 @@
           <t>14946</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>15604</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/leapindialtd/LIL07</t>
+          <t>https://www.moneycontrol.com/ipo/miscellaneous/leapindia/LIL07</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-08-13 10:35:31</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Technocraft Ventures Ltd</t>
+          <t>LEAP India Ltd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -957,31 +957,31 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>94</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>159</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14840</t>
+          <t>14946</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocraftventuresltd/TVL</t>
+          <t>https://www.moneycontrol.com/ipo/leapindialtd/LIL07</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -993,77 +993,85 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dhoot Transmission Ltd</t>
+          <t>Technocraft Ventures</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Aug 10, 2026</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Aug 12, 2026</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Aug 13, 2026</t>
-        </is>
-      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14807</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>14840</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>19880</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5040</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/dhoottransmissionltd/DTL02</t>
+          <t>https://www.moneycontrol.com/ipo/miscellaneous/technocraftventures/TVL</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-08-13 10:35:31</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics Ltd</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>Technocraft Ventures Ltd</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
@@ -1071,51 +1079,51 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aug 10, 2026</t>
+          <t>Aug 07, 2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Aug 11, 2026</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Aug 12, 2026</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Aug 13, 2026</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14526</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>39</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/molbiodiagnosticsltd/MDL02</t>
+          <t>https://www.moneycontrol.com/ipo/technocraftventuresltd/TVL</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1127,334 +1135,342 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food Ltd</t>
+          <t>Dhoot Transmission Ltd</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aug 11, 2026</t>
+          <t>Aug 10, 2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Aug 13, 2026</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Aug 14, 2026</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>871</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14980</t>
+          <t>14807</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>74</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/milkymistdairyfoodltd/MMD</t>
+          <t>https://www.moneycontrol.com/ipo/dhoottransmissionltd/DTL02</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-08-13 10:35:31</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering Ltd</t>
+          <t>Molbio Diagnostics Ltd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Aug 10, 2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Aug 12, 2026</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Aug 14, 2026</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>Aug 13, 2026</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>Aug 17, 2026</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Aug 19, 2026</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>807</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14820</t>
+          <t>14526</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>70</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/beharilalengineeringltd/BLE</t>
+          <t>https://www.moneycontrol.com/ipo/molbiodiagnosticsltd/MDL02</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-08-13 10:35:31</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shiprocket Ltd</t>
+          <t>Milky Mist Dairy Food Ltd</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 11, 2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Aug 13, 2026</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>Aug 14, 2026</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Aug 17, 2026</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>107</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14938</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shiprocketltd/SL26</t>
+          <t>https://www.moneycontrol.com/ipo/milkymistdairyfoodltd/MMD</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-13 10:35:31</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks Ltd</t>
+          <t>Behari Lal Engineering Ltd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>Aug 17, 2026</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Aug 19, 2026</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Aug 20, 2026</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Aug 24, 2026</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>57-60</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>14820</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/horizonindustrialparksltd/HIP01</t>
+          <t>https://www.moneycontrol.com/ipo/beharilalengineeringltd/BLE</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-08-13 10:35:31</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart Ltd</t>
+          <t>Shiprocket Ltd</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>Aug 17, 2026</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Aug 19, 2026</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Aug 20, 2026</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Aug 24, 2026</t>
-        </is>
-      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>190-201</t>
+          <t>97</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14874</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/lalithaajewellerymartltd/LJML</t>
+          <t>https://www.moneycontrol.com/ipo/shiprocketltd/SL26</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-08-13 10:35:31</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers Ltd</t>
+          <t>Horizon Industrial Parks Ltd</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1465,37 +1481,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>Aug 20, 2026</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Aug 21, 2026</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Aug 25, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>250</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>88-93</t>
+          <t>57-60</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1505,19 +1521,19 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shankeshjewellersltd/SJL01</t>
+          <t>https://www.moneycontrol.com/ipo/horizonindustrialparksltd/HIP01</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-08-13 10:35:31</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Ltd</t>
+          <t>Lalithaa Jewellery Mart Ltd</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1528,37 +1544,37 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Aug 20, 2026</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Aug 21, 2026</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Aug 25, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>342-360</t>
+          <t>190-201</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14874</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1568,19 +1584,19 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/sunshinepicturesltd/SPL13</t>
+          <t>https://www.moneycontrol.com/ipo/lalithaajewellerymartltd/LJML</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-08-13 10:35:31</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Shankesh Jewellers Ltd</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1591,33 +1607,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 20, 2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Aug 21, 2026</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>88-93</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1627,19 +1647,19 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/shankeshjewellersltd/SJL01</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Sunshine Pictures Ltd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1650,33 +1670,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 20, 2026</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Aug 21, 2026</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>342-360</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>14760</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1686,19 +1710,19 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/sunshinepicturesltd/SPL13</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Gaja Alternative Asset Management Ltd</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1709,33 +1733,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>Aug 24, 2026</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Aug 26, 2026</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>93</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>152-160</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1745,17 +1773,308 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/gajaalternativeassetmanagementltd/GAA</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2026-08-14 21:36:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Skyways Air Services</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Aug 24, 2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aug 27, 2026</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Aug 28, 2026</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sep 01, 2026</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>131-138</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>13800</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/skywaysairservices/S28</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2026-08-14 21:36:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Credent Connect N Care Ltd</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Aug 13, 2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aug 17, 2026</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>179-189</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>113400</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:43:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Mopshop Distribution Ltd</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aug 21, 2026</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Aug 24, 2026</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2026-08-14 21:36:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Q&amp;T Foods Ltd</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Aug 17, 2026</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:24:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q19"/>
+  <autoFilter ref="A1:Q24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-15 09:24:51</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-15 09:24:51</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-15 09:24:51</t>
         </is>
       </c>
     </row>
@@ -1340,9 +1340,9 @@
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1384,7 +1384,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-15 09:24:51</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-15 09:24:51</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-15 09:24:51</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-15 09:24:51</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-15 09:24:51</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-15 09:24:51</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-15 09:24:51</t>
         </is>
       </c>
     </row>
@@ -1932,13 +1932,21 @@
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>138</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-08-15 09:24:51</t>
+          <t>2026-08-15 21:04:54</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-08-15 09:24:51</t>
+          <t>2026-08-15 21:04:54</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-15 09:24:51</t>
+          <t>2026-08-15 21:04:54</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-08-15 09:24:51</t>
+          <t>2026-08-15 21:04:54</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-08-15 09:24:51</t>
+          <t>2026-08-15 21:04:54</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-08-15 09:24:51</t>
+          <t>2026-08-15 21:04:54</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-08-15 09:24:51</t>
+          <t>2026-08-15 21:04:54</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-08-15 09:24:51</t>
+          <t>2026-08-15 21:04:54</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-08-15 09:24:51</t>
+          <t>2026-08-15 21:04:54</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-15 09:24:51</t>
+          <t>2026-08-15 21:04:54</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-08-15 21:04:54</t>
+          <t>2026-08-16 09:29:34</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-08-15 21:04:54</t>
+          <t>2026-08-16 09:29:34</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-15 21:04:54</t>
+          <t>2026-08-16 09:29:34</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-08-15 21:04:54</t>
+          <t>2026-08-16 09:29:34</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-08-15 21:04:54</t>
+          <t>2026-08-16 09:29:34</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-08-15 21:04:54</t>
+          <t>2026-08-16 09:29:34</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-08-15 21:04:54</t>
+          <t>2026-08-16 09:29:34</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-08-15 21:04:54</t>
+          <t>2026-08-16 09:29:34</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-08-15 21:04:54</t>
+          <t>2026-08-16 09:29:34</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-15 21:04:54</t>
+          <t>2026-08-16 09:29:34</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-08-16 09:29:34</t>
+          <t>2026-08-16 21:05:31</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-08-16 09:29:34</t>
+          <t>2026-08-16 21:05:31</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-16 09:29:34</t>
+          <t>2026-08-16 21:05:31</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-08-16 09:29:34</t>
+          <t>2026-08-16 21:05:31</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-08-16 09:29:34</t>
+          <t>2026-08-16 21:05:31</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-08-16 09:29:34</t>
+          <t>2026-08-16 21:05:31</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-08-16 09:29:34</t>
+          <t>2026-08-16 21:05:31</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-08-16 09:29:34</t>
+          <t>2026-08-16 21:05:31</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-08-16 09:29:34</t>
+          <t>2026-08-16 21:05:31</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-16 09:29:34</t>
+          <t>2026-08-16 21:05:31</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1135,30 +1135,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dhoot Transmission Ltd</t>
+          <t>Dhoot Transmission</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Aug 10, 2026</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Aug 12, 2026</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Aug 13, 2026</t>
-        </is>
-      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Aug 17, 2026</t>
@@ -1190,19 +1178,19 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/dhoottransmissionltd/DTL02</t>
+          <t>https://www.moneycontrol.com/ipo/miscellaneous/dhoottransmission/DTL02</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-08-16 21:05:31</t>
+          <t>2026-08-17 09:32:55</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics Ltd</t>
+          <t>Dhoot Transmission Ltd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -1233,31 +1221,31 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>871</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14526</t>
+          <t>14807</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>74</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/molbiodiagnosticsltd/MDL02</t>
+          <t>https://www.moneycontrol.com/ipo/dhoottransmissionltd/DTL02</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1269,74 +1257,62 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food Ltd</t>
+          <t>Molbio Diagnostics</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Aug 11, 2026</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Aug 13, 2026</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Aug 14, 2026</t>
-        </is>
-      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>807</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14980</t>
+          <t>14526</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>70</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/milkymistdairyfoodltd/MMD</t>
+          <t>https://www.moneycontrol.com/ipo/miscellaneous/molbiodiagnostics/MDL02</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-16 21:05:31</t>
+          <t>2026-08-17 09:32:55</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering Ltd</t>
+          <t>Molbio Diagnostics Ltd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1347,51 +1323,51 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Aug 10, 2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Aug 12, 2026</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Aug 14, 2026</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>Aug 13, 2026</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>Aug 17, 2026</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Aug 19, 2026</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>807</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14820</t>
+          <t>14526</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>70</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/beharilalengineeringltd/BLE</t>
+          <t>https://www.moneycontrol.com/ipo/molbiodiagnosticsltd/MDL02</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1403,241 +1379,249 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shiprocket Ltd</t>
+          <t>Milky Mist Dairy Food Ltd</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 11, 2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Aug 13, 2026</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>Aug 14, 2026</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Aug 17, 2026</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>107</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14938</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shiprocketltd/SL26</t>
+          <t>https://www.moneycontrol.com/ipo/milkymistdairyfoodltd/MMD</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-17 09:32:55</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks Ltd</t>
+          <t>Behari Lal Engineering Ltd</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>Aug 17, 2026</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Aug 19, 2026</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Aug 20, 2026</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Aug 24, 2026</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>57-60</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>14820</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/horizonindustrialparksltd/HIP01</t>
+          <t>https://www.moneycontrol.com/ipo/beharilalengineeringltd/BLE</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-08-16 21:05:31</t>
+          <t>2026-08-17 09:32:55</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart Ltd</t>
+          <t>Shiprocket Ltd</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Aug 17, 2026</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Aug 19, 2026</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Aug 20, 2026</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Aug 24, 2026</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>190-201</t>
+          <t>97</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14874</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/lalithaajewellerymartltd/LJML</t>
+          <t>https://www.moneycontrol.com/ipo/shiprocketltd/SL26</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-08-16 21:05:31</t>
+          <t>2026-08-17 09:32:55</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers Ltd</t>
+          <t>Horizon Industrial Parks Ltd</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Aug 20, 2026</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Aug 21, 2026</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Aug 25, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>250</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>88-93</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1647,60 +1631,60 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shankeshjewellersltd/SJL01</t>
+          <t>https://www.moneycontrol.com/ipo/horizonindustrialparksltd/HIP01</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-08-16 21:05:31</t>
+          <t>2026-08-17 09:32:55</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Ltd</t>
+          <t>Lalithaa Jewellery Mart Ltd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Aug 20, 2026</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Aug 21, 2026</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Aug 25, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>342-360</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14874</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1710,19 +1694,19 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/sunshinepicturesltd/SPL13</t>
+          <t>https://www.moneycontrol.com/ipo/lalithaajewellerymartltd/LJML</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-08-16 21:05:31</t>
+          <t>2026-08-17 09:32:55</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management Ltd</t>
+          <t>Shankesh Jewellers Ltd</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1733,32 +1717,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Aug 20, 2026</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Aug 21, 2026</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Aug 24, 2026</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Aug 26, 2026</t>
+          <t>Aug 25, 2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>152-160</t>
+          <t>88-93</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1773,19 +1757,19 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/gajaalternativeassetmanagementltd/GAA</t>
+          <t>https://www.moneycontrol.com/ipo/shankeshjewellersltd/SJL01</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-08-16 21:05:31</t>
+          <t>2026-08-17 09:32:55</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Skyways Air Services</t>
+          <t>Sunshine Pictures Ltd</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1796,37 +1780,37 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aug 27, 2026</t>
+          <t>Aug 20, 2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 25, 2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>131-138</t>
+          <t>342-360</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>14760</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1836,19 +1820,19 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/skywaysairservices/S28</t>
+          <t>https://www.moneycontrol.com/ipo/sunshinepicturesltd/SPL13</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-16 21:05:31</t>
+          <t>2026-08-17 09:32:55</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Gaja Alternative Asset Management Ltd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1859,33 +1843,37 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Aug 24, 2026</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Aug 26, 2026</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>93</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>152-160</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1895,19 +1883,19 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/gajaalternativeassetmanagementltd/GAA</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-17 09:32:55</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Skyways Air Services</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1918,33 +1906,37 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Aug 27, 2026</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Aug 28, 2026</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sep 01, 2026</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>131-138</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>13800</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1954,19 +1946,19 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/skywaysairservices/S28</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-17 09:32:55</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1977,33 +1969,33 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -2013,19 +2005,19 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -2036,17 +2028,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2057,12 +2049,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>138</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -2072,17 +2064,135 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2026-08-14 21:36:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Q&amp;T Foods Ltd</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Aug 17, 2026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:24:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q24"/>
+  <autoFilter ref="A1:Q26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1419,34 +1419,18 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food Ltd</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Aug 11, 2026</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Aug 13, 2026</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Aug 14, 2026</t>
-        </is>
-      </c>
+          <t>Milky Mist Dairy Food</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Aug 18, 2026</t>
@@ -1478,22 +1462,26 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/milkymistdairyfoodltd/MMD</t>
+          <t>https://www.moneycontrol.com/ipo/consumer-food/milkymistdairyfood/MMD</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:52</t>
+          <t>2026-08-18 09:28:21</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering Ltd</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>Milky Mist Dairy Food Ltd</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
@@ -1501,51 +1489,51 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 11, 2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Aug 13, 2026</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>Aug 14, 2026</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Aug 17, 2026</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>107</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14820</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/beharilalengineeringltd/BLE</t>
+          <t>https://www.moneycontrol.com/ipo/milkymistdairyfoodltd/MMD</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1557,7 +1545,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Shiprocket Ltd</t>
+          <t>Behari Lal Engineering Ltd</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1588,110 +1576,110 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14938</t>
+          <t>14820</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shiprocketltd/SL26</t>
+          <t>https://www.moneycontrol.com/ipo/beharilalengineeringltd/BLE</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:52</t>
+          <t>2026-08-18 09:28:21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks Ltd</t>
+          <t>Shiprocket Ltd</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Aug 17, 2026</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Aug 19, 2026</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Aug 20, 2026</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Aug 24, 2026</t>
-        </is>
-      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>97</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/horizonindustrialparksltd/HIP01</t>
+          <t>https://www.moneycontrol.com/ipo/shiprocketltd/SL26</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:52</t>
+          <t>2026-08-18 09:28:21</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart Ltd</t>
+          <t>Horizon Industrial Parks Ltd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1722,17 +1710,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>250</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>14874</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1746,88 +1734,92 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/lalithaajewellerymartltd/LJML</t>
+          <t>https://www.moneycontrol.com/ipo/horizonindustrialparksltd/HIP01</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:52</t>
+          <t>2026-08-18 09:28:21</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers Ltd</t>
+          <t>Lalithaa Jewellery Mart Ltd</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Aug 20, 2026</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Aug 21, 2026</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Aug 25, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>88-93</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>14874</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shankeshjewellersltd/SJL01</t>
+          <t>https://www.moneycontrol.com/ipo/lalithaajewellerymartltd/LJML</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:52</t>
+          <t>2026-08-18 09:28:21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Ltd</t>
+          <t>Shankesh Jewellers Ltd</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1852,17 +1844,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>342-360</t>
+          <t>93</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1872,60 +1864,60 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/sunshinepicturesltd/SPL13</t>
+          <t>https://www.moneycontrol.com/ipo/shankeshjewellersltd/SJL01</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:52</t>
+          <t>2026-08-18 09:28:21</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management Ltd</t>
+          <t>Sunshine Pictures Ltd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Aug 20, 2026</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Aug 21, 2026</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Aug 24, 2026</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Aug 26, 2026</t>
+          <t>Aug 25, 2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>152-160</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>14760</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1935,19 +1927,19 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/gajaalternativeassetmanagementltd/GAA</t>
+          <t>https://www.moneycontrol.com/ipo/sunshinepicturesltd/SPL13</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:52</t>
+          <t>2026-08-18 09:28:21</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tempsens Instruments India Ltd</t>
+          <t>Gaja Alternative Asset Management Ltd</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1958,37 +1950,37 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Aug 20, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Aug 21, 2026</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Aug 24, 2026</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Aug 25, 2026</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Aug 26, 2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>93</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>285-300</t>
+          <t>152-160</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1998,19 +1990,19 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/tempsensinstrumentsindialtd/TII02</t>
+          <t>https://www.moneycontrol.com/ipo/gajaalternativeassetmanagementltd/GAA</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:52</t>
+          <t>2026-08-18 09:28:21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Skyways Air Services</t>
+          <t>Tempsens Instruments India Ltd</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -2021,37 +2013,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>Aug 20, 2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>Aug 24, 2026</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Aug 27, 2026</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>Aug 28, 2026</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Sep 01, 2026</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>131-138</t>
+          <t>285-300</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -2061,19 +2053,19 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/skywaysairservices/S28</t>
+          <t>https://www.moneycontrol.com/ipo/tempsensinstrumentsindialtd/TII02</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-08-17 21:10:52</t>
+          <t>2026-08-18 09:28:21</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Skyways Air Services</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -2084,33 +2076,37 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 27, 2026</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>Aug 28, 2026</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sep 01, 2026</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>131-138</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>13800</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -2120,19 +2116,19 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/skywaysairservices/S28</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-18 09:28:21</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -2143,33 +2139,33 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -2179,19 +2175,19 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -2202,28 +2198,28 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>138</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2238,19 +2234,19 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -2261,33 +2257,33 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>Aug 14, 2026</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2297,17 +2293,76 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:24:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q27"/>
+  <autoFilter ref="A1:Q28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-08-18 09:28:21</t>
+          <t>2026-08-18 21:16:38</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-08-18 09:28:21</t>
+          <t>2026-08-18 21:16:38</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-08-18 09:28:21</t>
+          <t>2026-08-18 21:16:38</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-08-18 09:28:21</t>
+          <t>2026-08-18 21:16:38</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,11 @@
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -1869,7 +1873,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-18 09:28:21</t>
+          <t>2026-08-18 21:16:38</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1926,11 @@
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -1932,7 +1940,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-08-18 09:28:21</t>
+          <t>2026-08-18 21:16:38</t>
         </is>
       </c>
     </row>
@@ -1995,7 +2003,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-08-18 09:28:21</t>
+          <t>2026-08-18 21:16:38</t>
         </is>
       </c>
     </row>
@@ -2058,14 +2066,14 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-08-18 09:28:21</t>
+          <t>2026-08-18 21:16:38</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Skyways Air Services</t>
+          <t>Augmont Enterprises Ltd</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -2076,37 +2084,37 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>Aug 27, 2026</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Aug 28, 2026</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>131-138</t>
+          <t>750-788</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -2116,19 +2124,19 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/skywaysairservices/S28</t>
+          <t>https://www.moneycontrol.com/ipo/augmontenterprisesltd/AEL13</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-08-18 09:28:21</t>
+          <t>2026-08-18 21:16:38</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Skyways Air Services</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -2139,33 +2147,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 27, 2026</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Aug 28, 2026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sep 01, 2026</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>131-138</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>13800</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -2175,19 +2187,19 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/skywaysairservices/S28</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-18 21:16:38</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -2198,33 +2210,33 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2234,19 +2246,19 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -2257,28 +2269,28 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>138</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2293,19 +2305,19 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -2316,33 +2328,33 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>Aug 14, 2026</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2352,17 +2364,76 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:24:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q28"/>
+  <autoFilter ref="A1:Q29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1545,30 +1545,18 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Behari Lal Engineering Ltd</t>
+          <t>Behari Lal Engineering</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Aug 12, 2026</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Aug 14, 2026</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Aug 17, 2026</t>
-        </is>
-      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Aug 19, 2026</t>
@@ -1600,19 +1588,19 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/beharilalengineeringltd/BLE</t>
+          <t>https://www.moneycontrol.com/ipo/metals-castingsforgings/beharilalengineering/BLE</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-08-18 21:16:38</t>
+          <t>2026-08-19 09:29:19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Shiprocket Ltd</t>
+          <t>Behari Lal Engineering Ltd</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1643,31 +1631,31 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14938</t>
+          <t>14820</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shiprocketltd/SL26</t>
+          <t>https://www.moneycontrol.com/ipo/beharilalengineeringltd/BLE</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1679,129 +1667,117 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks Ltd</t>
+          <t>Shiprocket</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Aug 17, 2026</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Aug 19, 2026</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Aug 20, 2026</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Aug 24, 2026</t>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>97</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/horizonindustrialparksltd/HIP01</t>
+          <t>https://www.moneycontrol.com/ipo/online-services/shiprocket/SL26</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-08-18 21:16:38</t>
+          <t>2026-08-19 09:29:19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart Ltd</t>
+          <t>Shiprocket Ltd</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Aug 17, 2026</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Aug 19, 2026</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Aug 20, 2026</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Aug 24, 2026</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>97</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14874</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>99</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/lalithaajewellerymartltd/LJML</t>
+          <t>https://www.moneycontrol.com/ipo/shiprocketltd/SL26</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1813,7 +1789,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers Ltd</t>
+          <t>Horizon Industrial Parks Ltd</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1824,37 +1800,37 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>Aug 20, 2026</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Aug 21, 2026</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Aug 25, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>250</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1868,19 +1844,19 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shankeshjewellersltd/SJL01</t>
+          <t>https://www.moneycontrol.com/ipo/horizonindustrialparksltd/HIP01</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-18 21:16:38</t>
+          <t>2026-08-19 09:29:19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Ltd</t>
+          <t>Lalithaa Jewellery Mart Ltd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1891,99 +1867,99 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Aug 20, 2026</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Aug 21, 2026</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Aug 25, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14874</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/sunshinepicturesltd/SPL13</t>
+          <t>https://www.moneycontrol.com/ipo/lalithaajewellerymartltd/LJML</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-08-18 21:16:38</t>
+          <t>2026-08-19 09:29:19</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management Ltd</t>
+          <t>Shankesh Jewellers Ltd</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Aug 20, 2026</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Aug 21, 2026</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Aug 24, 2026</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Aug 26, 2026</t>
+          <t>Aug 25, 2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>93</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>152-160</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1993,128 +1969,136 @@
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/gajaalternativeassetmanagementltd/GAA</t>
+          <t>https://www.moneycontrol.com/ipo/shankeshjewellersltd/SJL01</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-08-18 21:16:38</t>
+          <t>2026-08-19 09:29:19</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tempsens Instruments India Ltd</t>
+          <t>Sunshine Pictures Ltd</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>Aug 20, 2026</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Aug 24, 2026</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>Aug 21, 2026</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>Aug 25, 2026</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Aug 28, 2026</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>285-300</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>14760</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/tempsensinstrumentsindialtd/TII02</t>
+          <t>https://www.moneycontrol.com/ipo/sunshinepicturesltd/SPL13</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-08-18 21:16:38</t>
+          <t>2026-08-19 09:29:19</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Augmont Enterprises Ltd</t>
+          <t>Gaja Alternative Asset Management Ltd</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>Aug 21, 2026</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Aug 25, 2026</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aug 27, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 26, 2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>93</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>750-788</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>14972</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -2124,19 +2108,19 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/augmontenterprisesltd/AEL13</t>
+          <t>https://www.moneycontrol.com/ipo/gajaalternativeassetmanagementltd/GAA</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-08-18 21:16:38</t>
+          <t>2026-08-19 09:29:19</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Skyways Air Services</t>
+          <t>Tempsens Instruments India Ltd</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -2147,37 +2131,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>Aug 20, 2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>Aug 24, 2026</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Aug 27, 2026</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>Aug 28, 2026</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Sep 01, 2026</t>
-        </is>
-      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>131-138</t>
+          <t>285-300</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -2187,19 +2171,19 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/skywaysairservices/S28</t>
+          <t>https://www.moneycontrol.com/ipo/tempsensinstrumentsindialtd/TII02</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-08-18 21:16:38</t>
+          <t>2026-08-19 09:29:19</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Augmont Enterprises Ltd</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -2210,33 +2194,37 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 25, 2026</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>Aug 27, 2026</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Aug 31, 2026</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>750-788</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2246,19 +2234,19 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/augmontenterprisesltd/AEL13</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-19 09:29:19</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Skyways Air Services</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -2269,33 +2257,37 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Aug 27, 2026</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>Aug 28, 2026</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sep 01, 2026</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>131-138</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>13800</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2305,19 +2297,19 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/skywaysairservices/S28</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-19 09:29:19</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -2328,33 +2320,33 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2364,19 +2356,19 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -2387,17 +2379,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -2408,12 +2400,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>138</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2423,17 +2415,135 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>2026-08-14 21:36:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Q&amp;T Foods Ltd</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Aug 17, 2026</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:24:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q29"/>
+  <autoFilter ref="A1:Q31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1849,14 +1849,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-19 09:29:19</t>
+          <t>2026-08-19 21:16:43</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart Ltd</t>
+          <t>Lalithaa Jewellery Mart</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1904,26 +1904,26 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/lalithaajewellerymartltd/LJML</t>
+          <t>https://www.moneycontrol.com/ipo/lalithaajewellerymart/LJML</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-08-19 09:29:19</t>
+          <t>2026-08-19 21:16:43</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers Ltd</t>
+          <t>Lalithaa Jewellery Mart Ltd</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1934,51 +1934,51 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Aug 20, 2026</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Aug 21, 2026</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Aug 25, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>14874</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shankeshjewellersltd/SJL01</t>
+          <t>https://www.moneycontrol.com/ipo/lalithaajewellerymartltd/LJML</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -1990,7 +1990,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Ltd</t>
+          <t>Shankesh Jewellers</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -2021,43 +2021,43 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>93</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/sunshinepicturesltd/SPL13</t>
+          <t>https://www.moneycontrol.com/ipo/shankeshjewellers/SJL01</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-08-19 09:29:19</t>
+          <t>2026-08-19 21:16:43</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management Ltd</t>
+          <t>Shankesh Jewellers Ltd</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -2068,32 +2068,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Aug 20, 2026</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>Aug 21, 2026</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Aug 24, 2026</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Aug 26, 2026</t>
+          <t>Aug 25, 2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>93</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>160</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2103,12 +2103,16 @@
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/gajaalternativeassetmanagementltd/GAA</t>
+          <t>https://www.moneycontrol.com/ipo/shankeshjewellersltd/SJL01</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2120,133 +2124,141 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tempsens Instruments India Ltd</t>
+          <t>Sunshine Pictures Ltd</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>Aug 20, 2026</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Aug 24, 2026</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>Aug 21, 2026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>Aug 25, 2026</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Aug 28, 2026</t>
-        </is>
-      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>285-300</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>14760</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/tempsensinstrumentsindialtd/TII02</t>
+          <t>https://www.moneycontrol.com/ipo/sunshinepicturesltd/SPL13</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-08-19 09:29:19</t>
+          <t>2026-08-19 21:16:43</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Augmont Enterprises Ltd</t>
+          <t>Gaja Alternative Asset Management Ltd</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>Aug 21, 2026</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Aug 25, 2026</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aug 27, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 26, 2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>93</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>750-788</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>14972</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/augmontenterprisesltd/AEL13</t>
+          <t>https://www.moneycontrol.com/ipo/gajaalternativeassetmanagementltd/GAA</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-08-19 09:29:19</t>
+          <t>2026-08-19 21:16:43</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Skyways Air Services</t>
+          <t>Tempsens Instruments India Ltd</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -2257,37 +2269,37 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>Aug 20, 2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>Aug 24, 2026</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Aug 27, 2026</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>Aug 28, 2026</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Sep 01, 2026</t>
-        </is>
-      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>131-138</t>
+          <t>285-300</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2297,19 +2309,19 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/skywaysairservices/S28</t>
+          <t>https://www.moneycontrol.com/ipo/tempsensinstrumentsindialtd/TII02</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-08-19 09:29:19</t>
+          <t>2026-08-19 21:16:43</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Augmont Enterprises Ltd</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -2320,33 +2332,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 25, 2026</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Aug 27, 2026</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Aug 31, 2026</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>750-788</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2356,19 +2372,19 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/augmontenterprisesltd/AEL13</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-19 21:16:43</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Hy-Tech Engineers Ltd</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -2379,33 +2395,37 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Aug 27, 2026</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Aug 28, 2026</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sep 01, 2026</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>283</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>50-53</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2415,19 +2435,19 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/hy-techengineersltd/HEL01</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-19 21:16:43</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Skyways Air Services</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -2438,33 +2458,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 27, 2026</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>Aug 28, 2026</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sep 01, 2026</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>131-138</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>13800</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2474,19 +2498,19 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/skywaysairservices/S28</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-19 21:16:43</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Symbiotec Pharmalab Ltd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -2497,33 +2521,37 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Aug 27, 2026</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Aug 28, 2026</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sep 01, 2026</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>938-988</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>14820</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2533,17 +2561,253 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/symbiotecpharmalabltd/SPL14</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2026-08-19 21:16:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Credent Connect N Care Ltd</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Aug 13, 2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aug 17, 2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>179-189</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>113400</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:43:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Mopshop Distribution Ltd</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aug 21, 2026</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Aug 24, 2026</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2026-08-14 21:36:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Q&amp;T Foods Ltd</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Aug 17, 2026</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:24:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q31"/>
+  <autoFilter ref="A1:Q35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -1793,9 +1793,9 @@
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1837,7 +1837,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-19 21:16:43</t>
+          <t>2026-08-20 09:29:12</t>
         </is>
       </c>
     </row>
@@ -1860,9 +1860,9 @@
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1904,7 +1904,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>63</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-08-19 21:16:43</t>
+          <t>2026-08-20 09:29:12</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-08-19 21:16:43</t>
+          <t>2026-08-20 09:29:12</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-08-19 21:16:43</t>
+          <t>2026-08-20 09:29:12</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-08-19 21:16:43</t>
+          <t>2026-08-20 09:29:12</t>
         </is>
       </c>
     </row>
@@ -2262,9 +2262,9 @@
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>285-300</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-08-19 21:16:43</t>
+          <t>2026-08-20 09:29:12</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-08-19 21:16:43</t>
+          <t>2026-08-20 09:29:12</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-08-19 21:16:43</t>
+          <t>2026-08-20 09:29:12</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-08-19 21:16:43</t>
+          <t>2026-08-20 09:29:12</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-08-19 21:16:43</t>
+          <t>2026-08-20 09:29:12</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-20 09:29:12</t>
+          <t>2026-08-20 21:19:15</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-08-20 09:29:12</t>
+          <t>2026-08-20 21:19:15</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-08-20 09:29:12</t>
+          <t>2026-08-20 21:19:15</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>55</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-08-20 09:29:12</t>
+          <t>2026-08-20 21:19:15</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-08-20 09:29:12</t>
+          <t>2026-08-20 21:19:15</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,11 @@
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -2314,7 +2318,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-08-20 09:29:12</t>
+          <t>2026-08-20 21:19:15</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2381,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-08-20 09:29:12</t>
+          <t>2026-08-20 21:19:15</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2444,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-08-20 09:29:12</t>
+          <t>2026-08-20 21:19:15</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2507,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-08-20 09:29:12</t>
+          <t>2026-08-20 21:19:15</t>
         </is>
       </c>
     </row>
@@ -2566,14 +2570,14 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-08-20 09:29:12</t>
+          <t>2026-08-20 21:19:15</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Annu Projects Ltd</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -2584,35 +2588,27 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 25, 2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>179-189</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>113400</t>
-        </is>
-      </c>
+          <t>94-99</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
@@ -2620,19 +2616,19 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/annuprojectsltd/APL12</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-20 21:19:15</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -2643,33 +2639,33 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2679,19 +2675,19 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -2702,28 +2698,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>138</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2738,19 +2734,19 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -2761,33 +2757,33 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>Aug 14, 2026</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2797,17 +2793,76 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:24:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q35"/>
+  <autoFilter ref="A1:Q36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -1849,7 +1849,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-20 21:19:15</t>
+          <t>2026-08-21 09:32:02</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-08-20 21:19:15</t>
+          <t>2026-08-21 09:32:02</t>
         </is>
       </c>
     </row>
@@ -1994,9 +1994,9 @@
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2038,7 +2038,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-08-20 21:19:15</t>
+          <t>2026-08-21 09:32:02</t>
         </is>
       </c>
     </row>
@@ -2128,9 +2128,9 @@
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2172,7 +2172,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>106</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-08-20 21:19:15</t>
+          <t>2026-08-21 09:32:02</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-08-20 21:19:15</t>
+          <t>2026-08-21 09:32:02</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-08-20 21:19:15</t>
+          <t>2026-08-21 09:32:02</t>
         </is>
       </c>
     </row>
@@ -2329,9 +2329,9 @@
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>750-788</t>
+          <t>788</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-08-20 21:19:15</t>
+          <t>2026-08-21 09:32:02</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-08-20 21:19:15</t>
+          <t>2026-08-21 09:32:02</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-08-20 21:19:15</t>
+          <t>2026-08-21 09:32:02</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-08-20 21:19:15</t>
+          <t>2026-08-21 09:32:02</t>
         </is>
       </c>
     </row>
@@ -2601,14 +2601,26 @@
           <t>Aug 31, 2026</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sep 02, 2026</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>94-99</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>14949</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
@@ -2621,7 +2633,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-08-20 21:19:15</t>
+          <t>2026-08-21 09:32:02</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-21 09:32:02</t>
+          <t>2026-08-21 21:18:50</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-08-21 09:32:02</t>
+          <t>2026-08-21 21:18:50</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-08-21 09:32:02</t>
+          <t>2026-08-21 21:18:50</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-08-21 09:32:02</t>
+          <t>2026-08-21 21:18:50</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-08-21 09:32:02</t>
+          <t>2026-08-21 21:18:50</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-08-21 09:32:02</t>
+          <t>2026-08-21 21:18:50</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,11 @@
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -2381,7 +2385,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-08-21 09:32:02</t>
+          <t>2026-08-21 21:18:50</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2448,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-08-21 09:32:02</t>
+          <t>2026-08-21 21:18:50</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2511,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-08-21 09:32:02</t>
+          <t>2026-08-21 21:18:50</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2574,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-08-21 09:32:02</t>
+          <t>2026-08-21 21:18:50</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2637,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-08-21 09:32:02</t>
+          <t>2026-08-21 21:18:50</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2703,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Lumino Industries Ltd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -2710,35 +2714,27 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 27, 2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>138000</t>
-        </is>
-      </c>
+          <t>78-82</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -2746,19 +2742,19 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/luminoindustriesltd/LIL08</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-21 21:18:50</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -2769,28 +2765,28 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>138</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2805,19 +2801,19 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -2828,33 +2824,33 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>Aug 14, 2026</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2864,17 +2860,76 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:24:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q36"/>
+  <autoFilter ref="A1:Q37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -1849,7 +1849,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-21 21:18:50</t>
+          <t>2026-08-22 09:26:45</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-08-21 21:18:50</t>
+          <t>2026-08-22 09:26:45</t>
         </is>
       </c>
     </row>
@@ -2195,9 +2195,9 @@
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2239,7 +2239,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-08-21 21:18:50</t>
+          <t>2026-08-22 09:26:45</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-08-21 21:18:50</t>
+          <t>2026-08-22 09:26:45</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-08-21 21:18:50</t>
+          <t>2026-08-22 09:26:45</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-08-21 21:18:50</t>
+          <t>2026-08-22 09:26:45</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-08-21 21:18:50</t>
+          <t>2026-08-22 09:26:45</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-08-21 21:18:50</t>
+          <t>2026-08-22 09:26:45</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-08-21 21:18:50</t>
+          <t>2026-08-22 09:26:45</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-08-21 21:18:50</t>
+          <t>2026-08-22 09:26:45</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$Q$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1789,7 +1789,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Horizon Industrial Parks Ltd</t>
+          <t>Horizon Industrial Parks</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1798,16 +1798,8 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Aug 17, 2026</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Aug 19, 2026</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>Aug 20, 2026</t>
@@ -1844,19 +1836,19 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/horizonindustrialparksltd/HIP01</t>
+          <t>https://www.moneycontrol.com/ipo/horizonindustrialparks/HIP01</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-22 09:26:45</t>
+          <t>2026-08-22 21:05:13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart</t>
+          <t>Horizon Industrial Parks Ltd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1887,31 +1879,31 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>250</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14874</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/lalithaajewellerymart/LJML</t>
+          <t>https://www.moneycontrol.com/ipo/horizonindustrialparksltd/HIP01</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -1923,13 +1915,13 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart Ltd</t>
+          <t>Lalithaa Jewellery Mart</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1971,67 +1963,67 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>63</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/lalithaajewellerymartltd/LJML</t>
+          <t>https://www.moneycontrol.com/ipo/lalithaajewellerymart/LJML</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-08-19 09:29:19</t>
+          <t>2026-08-22 21:05:13</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers</t>
+          <t>Lalithaa Jewellery Mart Ltd</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>Aug 20, 2026</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Aug 21, 2026</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Aug 25, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>14874</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -2045,25 +2037,25 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shankeshjewellers/SJL01</t>
+          <t>https://www.moneycontrol.com/ipo/lalithaajewellerymartltd/LJML</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-08-21 21:18:50</t>
+          <t>2026-08-19 09:29:19</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers Ltd</t>
+          <t>Shankesh Jewellers</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2105,32 +2097,32 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shankeshjewellersltd/SJL01</t>
+          <t>https://www.moneycontrol.com/ipo/shankeshjewellers/SJL01</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-08-19 09:29:19</t>
+          <t>2026-08-21 21:18:50</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Ltd</t>
+          <t>Shankesh Jewellers Ltd</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2155,43 +2147,43 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>93</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/sunshinepicturesltd/SPL13</t>
+          <t>https://www.moneycontrol.com/ipo/shankeshjewellersltd/SJL01</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-08-21 21:18:50</t>
+          <t>2026-08-19 09:29:19</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Gaja Alternative Asset Management Ltd</t>
+          <t>Sunshine Pictures Ltd</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -2202,130 +2194,130 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Aug 20, 2026</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>Aug 21, 2026</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Aug 24, 2026</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Aug 26, 2026</t>
+          <t>Aug 25, 2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>14760</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>106</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/gajaalternativeassetmanagementltd/GAA</t>
+          <t>https://www.moneycontrol.com/ipo/sunshinepicturesltd/SPL13</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-08-22 09:26:45</t>
+          <t>2026-08-21 21:18:50</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tempsens Instruments India Ltd</t>
+          <t>Gaja Alternative Asset Management Ltd</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Aug 20, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Aug 21, 2026</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>Aug 24, 2026</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Aug 25, 2026</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Aug 26, 2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>93</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/tempsensinstrumentsindialtd/TII02</t>
+          <t>https://www.moneycontrol.com/ipo/gajaalternativeassetmanagementltd/GAA</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-08-22 09:26:45</t>
+          <t>2026-08-22 21:05:13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Augmont Enterprises Ltd</t>
+          <t>Tempsens Instruments India Ltd</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -2336,126 +2328,130 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Aug 20, 2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Aug 24, 2026</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>Aug 25, 2026</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Aug 27, 2026</t>
-        </is>
-      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>14972</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/augmontenterprisesltd/AEL13</t>
+          <t>https://www.moneycontrol.com/ipo/tempsensinstrumentsindialtd/TII02</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-08-22 09:26:45</t>
+          <t>2026-08-22 21:05:13</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Ltd</t>
+          <t>Augmont Enterprises Ltd</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>Aug 25, 2026</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>Aug 27, 2026</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Aug 28, 2026</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>50-53</t>
+          <t>788</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>14999</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/hy-techengineersltd/HEL01</t>
+          <t>https://www.moneycontrol.com/ipo/augmontenterprisesltd/AEL13</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-08-22 09:26:45</t>
+          <t>2026-08-22 21:05:13</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Skyways Air Services</t>
+          <t>Hy-Tech Engineers Ltd</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -2486,17 +2482,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>283</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>131-138</t>
+          <t>50-53</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2506,19 +2502,19 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/skywaysairservices/S28</t>
+          <t>https://www.moneycontrol.com/ipo/hy-techengineersltd/HEL01</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-08-22 09:26:45</t>
+          <t>2026-08-22 21:05:13</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab Ltd</t>
+          <t>Skyways Air Services</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -2549,17 +2545,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>938-988</t>
+          <t>131-138</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>14820</t>
+          <t>13800</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2569,19 +2565,19 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/symbiotecpharmalabltd/SPL14</t>
+          <t>https://www.moneycontrol.com/ipo/skywaysairservices/S28</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-08-22 09:26:45</t>
+          <t>2026-08-22 21:05:13</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Annu Projects Ltd</t>
+          <t>Symbiotec Pharmalab Ltd</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -2592,37 +2588,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Aug 25, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>Aug 27, 2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>Aug 28, 2026</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Aug 31, 2026</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>94-99</t>
+          <t>938-988</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>14949</t>
+          <t>14820</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2632,19 +2628,19 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/annuprojectsltd/APL12</t>
+          <t>https://www.moneycontrol.com/ipo/symbiotecpharmalabltd/SPL14</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-08-22 09:26:45</t>
+          <t>2026-08-22 21:05:13</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Annu Projects Ltd</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -2655,33 +2651,37 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 25, 2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>Aug 31, 2026</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sep 02, 2026</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>151</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>94-99</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>14949</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2691,12 +2691,12 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/annuprojectsltd/APL12</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-22 21:05:13</t>
         </is>
       </c>
     </row>
@@ -2727,14 +2727,26 @@
           <t>Sep 01, 2026</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sep 03, 2026</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>78-82</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>14924</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -2747,14 +2759,14 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-08-22 09:26:45</t>
+          <t>2026-08-22 21:05:13</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -2765,33 +2777,33 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2801,19 +2813,19 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -2824,28 +2836,28 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>138</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2860,19 +2872,19 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -2883,33 +2895,33 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>Aug 14, 2026</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2919,17 +2931,76 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:24:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q37"/>
+  <autoFilter ref="A1:Q38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-22 21:05:13</t>
+          <t>2026-08-23 09:31:18</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-08-22 21:05:13</t>
+          <t>2026-08-23 09:31:18</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-08-22 21:05:13</t>
+          <t>2026-08-23 09:31:18</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-08-22 21:05:13</t>
+          <t>2026-08-23 09:31:18</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-08-22 21:05:13</t>
+          <t>2026-08-23 09:31:18</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-08-22 21:05:13</t>
+          <t>2026-08-23 09:31:18</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-08-22 21:05:13</t>
+          <t>2026-08-23 09:31:18</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-08-22 21:05:13</t>
+          <t>2026-08-23 09:31:18</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-08-22 21:05:13</t>
+          <t>2026-08-23 09:31:18</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-08-22 21:05:13</t>
+          <t>2026-08-23 09:31:18</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -1793,9 +1793,9 @@
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1836,12 +1836,12 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/horizonindustrialparks/HIP01</t>
+          <t>https://www.moneycontrol.com/ipo/miscellaneous/horizonindustrialparks/HIP01</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-08-23 09:31:18</t>
+          <t>2026-08-24 09:36:01</t>
         </is>
       </c>
     </row>
@@ -1919,9 +1919,9 @@
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1970,12 +1970,12 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/lalithaajewellerymart/LJML</t>
+          <t>https://www.moneycontrol.com/ipo/diamondjewellery/lalithaajewellerymart/LJML</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-08-23 09:31:18</t>
+          <t>2026-08-24 09:36:01</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-08-21 21:18:50</t>
+          <t>2026-08-24 09:36:01</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-08-21 21:18:50</t>
+          <t>2026-08-24 09:36:01</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-08-23 09:31:18</t>
+          <t>2026-08-24 09:36:01</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-08-23 09:31:18</t>
+          <t>2026-08-24 09:36:01</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-08-23 09:31:18</t>
+          <t>2026-08-24 09:36:01</t>
         </is>
       </c>
     </row>
@@ -2455,9 +2455,9 @@
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>50-53</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-08-23 09:31:18</t>
+          <t>2026-08-24 09:36:01</t>
         </is>
       </c>
     </row>
@@ -2518,9 +2518,9 @@
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>131-138</t>
+          <t>138</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-08-23 09:31:18</t>
+          <t>2026-08-24 09:36:01</t>
         </is>
       </c>
     </row>
@@ -2581,9 +2581,9 @@
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>938-988</t>
+          <t>988</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-08-23 09:31:18</t>
+          <t>2026-08-24 09:36:01</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-08-23 09:31:18</t>
+          <t>2026-08-24 09:36:01</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-08-23 09:31:18</t>
+          <t>2026-08-24 09:36:01</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -1465,7 +1465,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-24 21:26:24</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-24 21:26:24</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
@@ -1577,9 +1577,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1628,12 +1628,12 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shankeshjewellers/SJL01</t>
+          <t>https://www.moneycontrol.com/ipo/diamondjewellery/shankeshjewellers/SJL01</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-24 21:26:24</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
@@ -1653,9 +1653,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1704,12 +1704,12 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/sunshinepicturesltd/SPL13</t>
+          <t>https://www.moneycontrol.com/ipo/miscellaneous/sunshinepictures/SPL13</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-24 21:26:24</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
@@ -1780,12 +1780,12 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/gajaalternativeassetmanagementltd/GAA</t>
+          <t>https://www.moneycontrol.com/ipo/gajaalternativeassetmanagement/GAA</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-08-24 21:26:24</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
@@ -1801,9 +1801,9 @@
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1845,19 +1845,19 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>184</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/tempsensinstrumentsindialtd/TII02</t>
+          <t>https://www.moneycontrol.com/ipo/tempsensinstrumentsindia/TII02</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-08-24 21:26:24</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
@@ -1917,19 +1917,19 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/augmontenterprisesltd/AEL13</t>
+          <t>https://www.moneycontrol.com/ipo/augmontenterprises/AEL13</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-08-24 21:26:24</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-08-24 21:26:24</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-08-24 21:26:24</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-08-24 21:26:24</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
@@ -2157,9 +2157,9 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>94-99</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-08-24 21:26:24</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-08-24 21:26:24</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-08-24 21:26:24</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-08-24 21:26:24</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-08-24 21:26:24</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-08-24 21:26:24</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-08-24 21:26:24</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -1465,7 +1465,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-25 21:30:33</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-25 21:30:33</t>
         </is>
       </c>
     </row>
@@ -1617,15 +1617,31 @@
           <t>14880</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>16480</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/diamondjewellery/shankeshjewellers/SJL01</t>
@@ -1633,7 +1649,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-25 21:30:33</t>
         </is>
       </c>
     </row>
@@ -1693,15 +1709,31 @@
           <t>14760</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>16236</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1476</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/miscellaneous/sunshinepictures/SPL13</t>
@@ -1709,7 +1741,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-25 21:30:33</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1817,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-25 21:30:33</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1889,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-25 21:30:33</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1949,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>42</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -1929,7 +1961,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-25 21:30:33</t>
         </is>
       </c>
     </row>
@@ -1989,7 +2021,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
@@ -2001,7 +2033,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-25 21:30:33</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2093,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -2073,7 +2105,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-25 21:30:33</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2177,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-25 21:30:33</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2231,11 @@
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
@@ -2209,7 +2245,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-25 21:30:33</t>
         </is>
       </c>
     </row>
@@ -2273,14 +2309,14 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-25 21:30:33</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rays of Belief Ltd</t>
+          <t>Priority Jewels Ltd</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -2292,37 +2328,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Aug 28, 2026</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>Sep 01, 2026</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Sep 03, 2026</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>Sep 02, 2026</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>Sep 04, 2026</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sep 08, 2026</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>227-239</t>
+          <t>190-200</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -2332,19 +2368,19 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/raysbeliefltd/RoB</t>
+          <t>https://www.moneycontrol.com/ipo/priorityjewelsltd/PJL01</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-25 21:30:33</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Rays of Belief Ltd</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -2356,27 +2392,39 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+          <t>Sep 04, 2026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sep 08, 2026</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>128-135</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>227-239</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>14818</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -2384,19 +2432,19 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/raysbeliefltd/RoB</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-25 21:30:33</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -2408,33 +2456,33 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -2444,19 +2492,19 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -2468,33 +2516,33 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -2504,19 +2552,19 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -2528,27 +2576,35 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>46-48</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -2556,19 +2612,19 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Priority Jewels Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -2594,13 +2650,21 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>190-200</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>46-48</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>144000</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -2608,7 +2672,7 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/priorityjewelsltd/PJL01</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2706,13 +2770,21 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>79-83</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>132800</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:30:33</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:30:33</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:30:33</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
@@ -1761,9 +1761,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1801,23 +1801,39 @@
           <t>14880</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>17205</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2325</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/gajaalternativeassetmanagement/GAA</t>
+          <t>https://www.moneycontrol.com/ipo/finance-investment/gajaalternativeassetmanagement/GAA</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:30:33</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1905,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-08-25 21:30:33</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
@@ -1905,9 +1921,9 @@
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1949,7 +1965,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>106</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -1961,7 +1977,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-08-25 21:30:33</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2037,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>135</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
@@ -2033,7 +2049,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-08-25 21:30:33</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2109,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -2105,7 +2121,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-08-25 21:30:33</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2181,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
@@ -2177,7 +2193,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-08-25 21:30:33</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2249,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -2245,7 +2261,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-08-25 21:30:33</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
@@ -2257,9 +2273,9 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2289,7 +2305,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>78-82</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2299,7 +2315,11 @@
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
@@ -2309,14 +2329,14 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-08-25 21:30:33</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Priority Jewels Ltd</t>
+          <t>ESDS Software Solution Ltd</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -2348,17 +2368,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>190-200</t>
+          <t>408-429</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -2368,19 +2388,19 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/priorityjewelsltd/PJL01</t>
+          <t>https://www.moneycontrol.com/ipo/esdssoftwaresolutionltd/ESSL</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-08-25 21:30:33</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rays of Belief Ltd</t>
+          <t>Priority Jewels Ltd</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -2392,37 +2412,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Aug 28, 2026</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>Sep 01, 2026</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Sep 03, 2026</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>Sep 02, 2026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>Sep 04, 2026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Sep 08, 2026</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>227-239</t>
+          <t>190-200</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -2432,19 +2452,19 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/raysbeliefltd/RoB</t>
+          <t>https://www.moneycontrol.com/ipo/priorityjewelsltd/PJL01</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-08-25 21:30:33</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Rays of Belief Ltd</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -2456,33 +2476,37 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Sep 04, 2026</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sep 08, 2026</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>62</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>227-239</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>14818</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -2492,19 +2516,19 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/raysbeliefltd/RoB</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -2516,33 +2540,33 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -2552,19 +2576,19 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -2576,33 +2600,33 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2612,19 +2636,19 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Deepa Jewellers Ltd</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -2636,35 +2660,27 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>46-48</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>144000</t>
-        </is>
-      </c>
+          <t>168-177</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -2672,19 +2688,19 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/deepajewellersltd/DJL</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -2696,35 +2712,27 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>138000</t>
-        </is>
-      </c>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -2732,19 +2740,19 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -2756,33 +2764,33 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2792,19 +2800,19 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -2816,33 +2824,33 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2852,17 +2860,249 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:29:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Purple Style Labs Ltd</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aug 31, 2026</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sep 02, 2026</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sep 03, 2026</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>546-575</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:43:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Q&amp;T Foods Ltd</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Aug 17, 2026</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:24:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Shanti Inorganics Ltd</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aug 31, 2026</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Sep 02, 2026</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sep 03, 2026</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>79-83</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>132800</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:29:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R33"/>
+  <autoFilter ref="A1:R37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -1649,7 +1649,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-28 20:53:27</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-28 20:53:27</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-28 20:53:27</t>
         </is>
       </c>
     </row>
@@ -1849,9 +1849,9 @@
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1889,23 +1889,39 @@
           <t>15000</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>31700</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>16700</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/tempsensinstrumentsindia/TII02</t>
+          <t>https://www.moneycontrol.com/ipo/engineering-industrial-equipments/tempsensinstrumentsindia/TII02</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-28 20:53:27</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1993,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-28 20:53:27</t>
         </is>
       </c>
     </row>
@@ -1993,9 +2009,9 @@
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2037,7 +2053,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>244</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
@@ -2049,7 +2065,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-28 20:53:27</t>
         </is>
       </c>
     </row>
@@ -2065,9 +2081,9 @@
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2109,7 +2125,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>71</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -2121,7 +2137,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-28 20:53:27</t>
         </is>
       </c>
     </row>
@@ -2137,9 +2153,9 @@
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2181,7 +2197,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>71</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
@@ -2193,7 +2209,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-28 20:53:27</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2265,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -2261,7 +2277,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-28 20:53:27</t>
         </is>
       </c>
     </row>
@@ -2317,7 +2333,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -2329,7 +2345,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-28 20:53:27</t>
         </is>
       </c>
     </row>
@@ -2341,9 +2357,9 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2373,7 +2389,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>408-429</t>
+          <t>429</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2383,7 +2399,11 @@
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
@@ -2393,7 +2413,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-28 20:53:27</t>
         </is>
       </c>
     </row>
@@ -2405,9 +2425,9 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2437,7 +2457,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>190-200</t>
+          <t>200</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2447,7 +2467,11 @@
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
@@ -2457,14 +2481,14 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-28 20:53:27</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rays of Belief Ltd</t>
+          <t>Deepa Jewellers Ltd</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -2496,17 +2520,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>227-239</t>
+          <t>168-177</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>14868</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -2516,19 +2540,19 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/raysbeliefltd/RoB</t>
+          <t>https://www.moneycontrol.com/ipo/deepajewellersltd/DJL</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-28 20:53:27</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Rays of Belief Ltd</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -2540,33 +2564,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Sep 04, 2026</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sep 08, 2026</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>62</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>227-239</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>14818</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -2576,19 +2604,19 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/raysbeliefltd/RoB</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-28 20:53:27</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -2600,33 +2628,33 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2636,19 +2664,19 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Deepa Jewellers Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -2660,27 +2688,35 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>168-177</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>179-189</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>113400</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -2688,12 +2724,12 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/deepajewellersltd/DJL</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
@@ -2726,13 +2762,21 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>118000</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -2917,7 +2961,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-28 20:53:27</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -1649,7 +1649,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-28 20:53:27</t>
+          <t>2026-08-29 15:35:29</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-28 20:53:27</t>
+          <t>2026-08-29 15:35:29</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-08-28 20:53:27</t>
+          <t>2026-08-29 15:35:29</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-08-28 20:53:27</t>
+          <t>2026-08-29 15:35:29</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-08-28 20:53:27</t>
+          <t>2026-08-29 15:35:29</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-08-28 20:53:27</t>
+          <t>2026-08-29 15:35:29</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-08-28 20:53:27</t>
+          <t>2026-08-29 15:35:29</t>
         </is>
       </c>
     </row>
@@ -2221,9 +2221,9 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2265,7 +2265,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-08-28 20:53:27</t>
+          <t>2026-08-29 15:35:29</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-08-28 20:53:27</t>
+          <t>2026-08-29 15:35:29</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-08-28 20:53:27</t>
+          <t>2026-08-29 15:35:29</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-08-28 20:53:27</t>
+          <t>2026-08-29 15:35:29</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-08-28 20:53:27</t>
+          <t>2026-08-29 15:35:29</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-08-28 20:53:27</t>
+          <t>2026-08-29 15:35:29</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-08-28 20:53:27</t>
+          <t>2026-08-29 15:35:29</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -1649,7 +1649,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-29 15:35:29</t>
+          <t>2026-08-30 14:44:43</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-29 15:35:29</t>
+          <t>2026-08-30 14:44:43</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-08-29 15:35:29</t>
+          <t>2026-08-30 14:44:43</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-08-29 15:35:29</t>
+          <t>2026-08-30 14:44:43</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-08-29 15:35:29</t>
+          <t>2026-08-30 14:44:43</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-08-29 15:35:29</t>
+          <t>2026-08-30 14:44:43</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-08-29 15:35:29</t>
+          <t>2026-08-30 14:44:43</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-08-29 15:35:29</t>
+          <t>2026-08-30 14:44:43</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-08-29 15:35:29</t>
+          <t>2026-08-30 14:44:43</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-08-29 15:35:29</t>
+          <t>2026-08-30 14:44:43</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-08-29 15:35:29</t>
+          <t>2026-08-30 14:44:43</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-08-29 15:35:29</t>
+          <t>2026-08-30 14:44:43</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-08-29 15:35:29</t>
+          <t>2026-08-30 14:44:43</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-08-29 15:35:29</t>
+          <t>2026-08-30 14:44:43</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -1741,7 +1741,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-30 14:44:43</t>
+          <t>2026-08-31 15:16:14</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-08-30 14:44:43</t>
+          <t>2026-08-31 15:16:14</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-08-30 14:44:43</t>
+          <t>2026-08-31 15:16:14</t>
         </is>
       </c>
     </row>
@@ -1937,9 +1937,9 @@
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1988,12 +1988,12 @@
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/augmontenterprises/AEL13</t>
+          <t>https://www.moneycontrol.com/ipo/trading/augmontenterprises/AEL13</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-08-30 14:44:43</t>
+          <t>2026-08-31 15:16:14</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-08-30 14:44:43</t>
+          <t>2026-08-31 15:16:14</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-08-30 14:44:43</t>
+          <t>2026-08-31 15:16:14</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-08-28 20:53:27</t>
+          <t>2026-08-31 15:16:14</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-08-30 14:44:43</t>
+          <t>2026-08-31 15:16:14</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-08-30 14:44:43</t>
+          <t>2026-08-31 15:16:14</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-08-30 14:44:43</t>
+          <t>2026-08-31 15:16:14</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-08-30 14:44:43</t>
+          <t>2026-08-31 15:16:14</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-08-30 14:44:43</t>
+          <t>2026-08-31 15:16:14</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-08-30 14:44:43</t>
+          <t>2026-08-31 15:16:14</t>
         </is>
       </c>
     </row>
@@ -2921,9 +2921,9 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2945,13 +2945,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>546-575</t>
+          <t>575</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
@@ -2961,7 +2965,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-08-30 14:44:43</t>
+          <t>2026-08-31 15:16:14</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2009,9 +2009,9 @@
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2049,23 +2049,39 @@
           <t>14999</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>21225</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>244</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>6226</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/hy-techengineersltd/HEL01</t>
+          <t>https://www.moneycontrol.com/ipo/miscellaneous/hy-techengineers/HEL01</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-08-31 15:16:14</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
@@ -2081,9 +2097,9 @@
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2121,23 +2137,39 @@
           <t>13800</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>12400</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>-1400</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/skywaysairservices/S28</t>
+          <t>https://www.moneycontrol.com/ipo/logistics/skywaysairservices/S28</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-08-31 15:16:14</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
@@ -2153,9 +2185,9 @@
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2193,23 +2225,39 @@
           <t>14820</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>14820</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/symbiotecpharmalabltd/SPL14</t>
+          <t>https://www.moneycontrol.com/ipo/miscellaneous/symbiotecpharmalab/SPL14</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-08-31 15:16:14</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
@@ -2221,9 +2269,9 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2272,12 +2320,12 @@
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/annuprojectsltd/APL12</t>
+          <t>https://www.moneycontrol.com/ipo/construction-infrastructure/annuprojects/APL12</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-08-31 15:16:14</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
@@ -2289,9 +2337,9 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2333,7 +2381,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -2345,7 +2393,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-08-31 15:16:14</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
@@ -2357,9 +2405,9 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2401,7 +2449,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>136</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
@@ -2413,7 +2461,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-08-31 15:16:14</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
@@ -2425,9 +2473,9 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2469,7 +2517,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
@@ -2481,7 +2529,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-08-31 15:16:14</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
@@ -2493,9 +2541,9 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2525,7 +2573,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>168-177</t>
+          <t>177</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2535,7 +2583,11 @@
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
@@ -2545,7 +2597,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-08-31 15:16:14</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
@@ -2557,9 +2609,9 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2589,7 +2641,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>227-239</t>
+          <t>239</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2599,7 +2651,11 @@
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
@@ -2609,14 +2665,14 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-08-31 15:16:14</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Veegaland Developers Ltd</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -2628,33 +2684,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 10, 2026</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 15, 2026</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Sep 16, 2026</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>107</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>130-140</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2664,19 +2724,19 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/veegalanddevelopersltd/VDL02</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -2688,33 +2748,33 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2724,19 +2784,19 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -2748,33 +2808,33 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2784,19 +2844,19 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -2808,33 +2868,33 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2844,19 +2904,19 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -2868,33 +2928,33 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2904,135 +2964,135 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>Sep 01, 2026</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>Sep 02, 2026</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Sep 03, 2026</t>
-        </is>
-      </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>46-48</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>144000</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-08-31 15:16:14</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>138000</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -3044,33 +3104,33 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -3080,19 +3140,19 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Shanti Inorganics Ltd</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -3104,33 +3164,33 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>79-83</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>132800</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -3140,17 +3200,77 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:29:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R37"/>
+  <autoFilter ref="A1:R38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-03 13:33:45</t>
         </is>
       </c>
     </row>
@@ -2252,12 +2252,12 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/miscellaneous/symbiotecpharmalab/SPL14</t>
+          <t>https://www.moneycontrol.com/ipo/pharmaceuticalsdrugs/symbiotecpharmalab/SPL14</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-03 13:33:45</t>
         </is>
       </c>
     </row>
@@ -2309,15 +2309,31 @@
           <t>14949</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>10872</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-4077</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-27</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/construction-infrastructure/annuprojects/APL12</t>
@@ -2325,7 +2341,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-03 13:33:45</t>
         </is>
       </c>
     </row>
@@ -2337,9 +2353,9 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2388,12 +2404,12 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/luminoindustriesltd/LIL08</t>
+          <t>https://www.moneycontrol.com/ipo/cables/luminoindustries/LIL08</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-03 13:33:45</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2477,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-03 13:33:45</t>
         </is>
       </c>
     </row>
@@ -2524,12 +2540,12 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/priorityjewelsltd/PJL01</t>
+          <t>https://www.moneycontrol.com/ipo/priorityjewels/PJL01</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-03 13:33:45</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2601,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
@@ -2597,7 +2613,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-03 13:33:45</t>
         </is>
       </c>
     </row>
@@ -2653,26 +2669,26 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/raysbeliefltd/RoB</t>
+          <t>https://www.moneycontrol.com/ipo/raysbelief/RoB</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-03 13:33:45</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Veegaland Developers Ltd</t>
+          <t>Pranav Constructions Ltd</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -2684,37 +2700,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>Sep 07, 2026</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Sep 09, 2026</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>Sep 10, 2026</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Sep 15, 2026</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Sep 16, 2026</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sep 18, 2026</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>130-140</t>
+          <t>118-124</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>14980</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2724,19 +2740,19 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/veegalanddevelopersltd/VDL02</t>
+          <t>https://www.moneycontrol.com/ipo/pranavconstructionsltd/PCL02</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-03 13:33:45</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Veegaland Developers Ltd</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -2748,33 +2764,37 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 10, 2026</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 15, 2026</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Sep 16, 2026</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>107</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>130-140</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2784,19 +2804,19 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/veegalanddevelopersltd/VDL02</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-03 13:33:45</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -2808,33 +2828,33 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2844,19 +2864,19 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -2868,33 +2888,33 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2904,19 +2924,19 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -2928,33 +2948,33 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2964,19 +2984,19 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -2988,33 +3008,33 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -3024,135 +3044,135 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>Sep 01, 2026</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>Sep 02, 2026</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Sep 03, 2026</t>
-        </is>
-      </c>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>46-48</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>144000</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>138000</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -3164,33 +3184,33 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -3200,19 +3220,19 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Shanti Inorganics Ltd</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -3224,33 +3244,33 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>79-83</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>132800</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -3260,17 +3280,77 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:29:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R38"/>
+  <autoFilter ref="A1:R39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -56,12 +56,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDE68A"/>
+        <fgColor rgb="FFBFDBFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBFDBFE"/>
+        <fgColor rgb="FFFDE68A"/>
       </patternFill>
     </fill>
   </fills>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R39"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2393,15 +2393,31 @@
           <t>14924</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>20020</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>5096</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/cables/luminoindustries/LIL08</t>
@@ -2409,7 +2425,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-03 13:33:45</t>
+          <t>2026-09-04 13:29:10</t>
         </is>
       </c>
     </row>
@@ -2421,9 +2437,9 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2472,12 +2488,12 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/esdssoftwaresolutionltd/ESSL</t>
+          <t>https://www.moneycontrol.com/ipo/miscellaneous/esdssoftwaresolution/ESSL</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-03 13:33:45</t>
+          <t>2026-09-04 13:29:10</t>
         </is>
       </c>
     </row>
@@ -2489,9 +2505,9 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2540,12 +2556,12 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/priorityjewels/PJL01</t>
+          <t>https://www.moneycontrol.com/ipo/diamondjewellery/priorityjewels/PJL01</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-03 13:33:45</t>
+          <t>2026-09-04 13:29:10</t>
         </is>
       </c>
     </row>
@@ -2557,9 +2573,9 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2601,7 +2617,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>43</t>
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
@@ -2613,7 +2629,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-03 13:33:45</t>
+          <t>2026-09-04 13:29:10</t>
         </is>
       </c>
     </row>
@@ -2625,9 +2641,9 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2669,7 +2685,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>108</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
@@ -2681,7 +2697,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-03 13:33:45</t>
+          <t>2026-09-04 13:29:10</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2709,7 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
@@ -2745,56 +2761,56 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-03 13:33:45</t>
+          <t>2026-09-04 13:29:10</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Veegaland Developers Ltd</t>
+          <t>Glass Wall Systems India Ltd</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>Sep 08, 2026</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>Sep 10, 2026</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Sep 15, 2026</t>
-        </is>
-      </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>Sep 11, 2026</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>Sep 16, 2026</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sep 18, 2026</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>82</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>130-140</t>
+          <t>172-182</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>14980</t>
+          <t>14924</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2804,57 +2820,61 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/veegalanddevelopersltd/VDL02</t>
+          <t>https://www.moneycontrol.com/ipo/glasswallsystemsindialtd/GWSIL</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-03 13:33:45</t>
+          <t>2026-09-04 13:29:10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Kanohar Electricals Ltd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 08, 2026</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 10, 2026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Sep 11, 2026</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sep 16, 2026</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>601-632</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>14536</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2864,57 +2884,61 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/kanoharelectricalsltd/KEL09</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-04 13:29:10</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Prasol Chemicals Ltd</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Sep 08, 2026</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 10, 2026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Sep 11, 2026</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sep 16, 2026</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>643-676</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>14872</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2924,57 +2948,61 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/prasolchemicalsltd/PCL03</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-09-04 13:29:10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Asset Reconstruction Company India Ltd</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 09, 2026</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 11, 2026</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>107</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>132-139</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>14873</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2984,57 +3012,61 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/assetreconstructioncompanyindialtd/ARCIL</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-09-04 13:29:10</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Veegaland Developers Ltd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 10, 2026</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 15, 2026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Sep 16, 2026</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>107</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>130-140</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -3044,24 +3076,24 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/veegalanddevelopersltd/VDL02</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-09-04 13:29:10</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
@@ -3084,17 +3116,17 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -3104,7 +3136,7 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3116,101 +3148,105 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>179-189</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>113400</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -3220,57 +3256,57 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -3280,57 +3316,57 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -3340,17 +3376,253 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:29:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Purple Style Labs Ltd</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aug 31, 2026</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Sep 02, 2026</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sep 03, 2026</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:25:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Q&amp;T Foods Ltd</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Aug 17, 2026</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:24:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Shanti Inorganics Ltd</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aug 31, 2026</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Sep 02, 2026</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sep 03, 2026</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>79-83</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>132800</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:29:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R39"/>
+  <autoFilter ref="A1:R43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R43"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-04 13:29:10</t>
+          <t>2026-09-05 13:10:47</t>
         </is>
       </c>
     </row>
@@ -2477,15 +2477,31 @@
           <t>14586</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>757</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>25738</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>136</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>11152</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/miscellaneous/esdssoftwaresolution/ESSL</t>
@@ -2493,7 +2509,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-04 13:29:10</t>
+          <t>2026-09-05 13:10:47</t>
         </is>
       </c>
     </row>
@@ -2545,15 +2561,31 @@
           <t>15000</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>17250</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/diamondjewellery/priorityjewels/PJL01</t>
@@ -2561,7 +2593,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-04 13:29:10</t>
+          <t>2026-09-05 13:10:47</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2661,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-04 13:29:10</t>
+          <t>2026-09-05 13:10:47</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2729,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-04 13:29:10</t>
+          <t>2026-09-05 13:10:47</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2793,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-04 13:29:10</t>
+          <t>2026-09-05 13:10:47</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2857,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-04 13:29:10</t>
+          <t>2026-09-05 13:10:47</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2921,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-04 13:29:10</t>
+          <t>2026-09-05 13:10:47</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2985,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-04 13:29:10</t>
+          <t>2026-09-05 13:10:47</t>
         </is>
       </c>
     </row>
@@ -3017,14 +3049,14 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-04 13:29:10</t>
+          <t>2026-09-05 13:10:47</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Veegaland Developers Ltd</t>
+          <t>Karamtara Engineering Ltd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -3036,37 +3068,37 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sep 10, 2026</t>
+          <t>Sep 09, 2026</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>Sep 11, 2026</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>Sep 15, 2026</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Sep 16, 2026</t>
-        </is>
-      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>130-140</t>
+          <t>241-254</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>14980</t>
+          <t>14986</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -3076,19 +3108,19 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/veegalanddevelopersltd/VDL02</t>
+          <t>https://www.moneycontrol.com/ipo/karamtaraengineeringltd/K05</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-04 13:29:10</t>
+          <t>2026-09-05 13:10:47</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Lcc Projects Ltd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -3100,33 +3132,37 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 09, 2026</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 11, 2026</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>102</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>139-146</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>14892</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -3136,19 +3172,19 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/lccprojectsltd/LPL02</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-05 13:10:47</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Manipal Payment and Identity Solutions Ltd</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -3160,33 +3196,37 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Sep 09, 2026</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 11, 2026</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>322-339</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>14916</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -3196,19 +3236,19 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/manipalpaymentidentitysolutionsltd/MPISL</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-09-05 13:10:47</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Rentomojo Ltd</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -3220,33 +3260,37 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 09, 2026</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 11, 2026</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>384-404</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>14948</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -3256,19 +3300,19 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/rentomojoltd/RL10</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-09-05 13:10:47</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Veegaland Developers Ltd</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -3280,33 +3324,37 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 10, 2026</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 15, 2026</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Sep 16, 2026</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>107</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>130-140</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -3316,19 +3364,19 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/veegalanddevelopersltd/VDL02</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-09-05 13:10:47</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -3356,17 +3404,17 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -3376,7 +3424,7 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3388,63 +3436,67 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>179-189</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>113400</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -3456,33 +3508,33 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -3492,19 +3544,19 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -3516,33 +3568,33 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -3552,19 +3604,19 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -3576,33 +3628,33 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -3612,17 +3664,253 @@
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:29:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Purple Style Labs Ltd</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aug 31, 2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Sep 02, 2026</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Sep 03, 2026</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:25:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Q&amp;T Foods Ltd</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Aug 17, 2026</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:24:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Shanti Inorganics Ltd</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aug 31, 2026</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Sep 02, 2026</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sep 03, 2026</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>79-83</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>132800</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:29:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R43"/>
+  <autoFilter ref="A1:R47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -2425,7 +2425,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-05 13:10:47</t>
+          <t>2026-09-05 22:51:13</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-05 13:10:47</t>
+          <t>2026-09-05 22:51:13</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-05 13:10:47</t>
+          <t>2026-09-05 22:51:13</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-05 13:10:47</t>
+          <t>2026-09-05 22:51:13</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-05 13:10:47</t>
+          <t>2026-09-05 22:51:13</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-05 13:10:47</t>
+          <t>2026-09-05 22:51:13</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-05 13:10:47</t>
+          <t>2026-09-05 22:51:13</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-05 13:10:47</t>
+          <t>2026-09-05 22:51:13</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-05 13:10:47</t>
+          <t>2026-09-05 22:51:13</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-05 13:10:47</t>
+          <t>2026-09-05 22:51:13</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-05 13:10:47</t>
+          <t>2026-09-05 22:51:13</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-05 13:10:47</t>
+          <t>2026-09-05 22:51:13</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-05 13:10:47</t>
+          <t>2026-09-05 22:51:13</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-05 13:10:47</t>
+          <t>2026-09-05 22:51:13</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-05 13:10:47</t>
+          <t>2026-09-05 22:51:13</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -2425,7 +2425,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-05 22:51:13</t>
+          <t>2026-09-06 13:24:48</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-05 22:51:13</t>
+          <t>2026-09-06 13:24:48</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-05 22:51:13</t>
+          <t>2026-09-06 13:24:48</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-05 22:51:13</t>
+          <t>2026-09-06 13:24:48</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-05 22:51:13</t>
+          <t>2026-09-06 13:24:48</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-05 22:51:13</t>
+          <t>2026-09-06 13:24:48</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-05 22:51:13</t>
+          <t>2026-09-06 13:24:48</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-05 22:51:13</t>
+          <t>2026-09-06 13:24:48</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-05 22:51:13</t>
+          <t>2026-09-06 13:24:48</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-05 22:51:13</t>
+          <t>2026-09-06 13:24:48</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-05 22:51:13</t>
+          <t>2026-09-06 13:24:48</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-05 22:51:13</t>
+          <t>2026-09-06 13:24:48</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-05 22:51:13</t>
+          <t>2026-09-06 13:24:48</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-05 22:51:13</t>
+          <t>2026-09-06 13:24:48</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-05 22:51:13</t>
+          <t>2026-09-06 13:24:48</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -2425,7 +2425,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-06 13:24:48</t>
+          <t>2026-09-06 23:06:30</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-06 13:24:48</t>
+          <t>2026-09-06 23:06:30</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-06 13:24:48</t>
+          <t>2026-09-06 23:06:30</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-06 13:24:48</t>
+          <t>2026-09-06 23:06:30</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-06 13:24:48</t>
+          <t>2026-09-06 23:06:30</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-06 13:24:48</t>
+          <t>2026-09-06 23:06:30</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-06 13:24:48</t>
+          <t>2026-09-06 23:06:30</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-06 13:24:48</t>
+          <t>2026-09-06 23:06:30</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-06 13:24:48</t>
+          <t>2026-09-06 23:06:30</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-06 13:24:48</t>
+          <t>2026-09-06 23:06:30</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-06 13:24:48</t>
+          <t>2026-09-06 23:06:30</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-06 13:24:48</t>
+          <t>2026-09-06 23:06:30</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-06 13:24:48</t>
+          <t>2026-09-06 23:06:30</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-06 13:24:48</t>
+          <t>2026-09-06 23:06:30</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-06 13:24:48</t>
+          <t>2026-09-06 23:06:30</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -56,12 +56,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBFDBFE"/>
+        <fgColor rgb="FFFDE68A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDE68A"/>
+        <fgColor rgb="FFBFDBFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-06 23:06:30</t>
+          <t>2026-09-07 13:49:18</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-06 23:06:30</t>
+          <t>2026-09-07 13:49:18</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-06 23:06:30</t>
+          <t>2026-09-07 13:49:18</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>118-124</t>
+          <t>124</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-06 23:06:30</t>
+          <t>2026-09-07 13:49:18</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-06 23:06:30</t>
+          <t>2026-09-07 13:49:18</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-06 23:06:30</t>
+          <t>2026-09-07 13:49:18</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-06 23:06:30</t>
+          <t>2026-09-07 13:49:18</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-06 23:06:30</t>
+          <t>2026-09-07 13:49:18</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-06 23:06:30</t>
+          <t>2026-09-07 13:49:18</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-06 23:06:30</t>
+          <t>2026-09-07 13:49:18</t>
         </is>
       </c>
     </row>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-06 23:06:30</t>
+          <t>2026-09-07 13:49:18</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-06 23:06:30</t>
+          <t>2026-09-07 13:49:18</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-06 23:06:30</t>
+          <t>2026-09-07 13:49:18</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Upcoming</t>
         </is>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:R50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2605,9 +2605,9 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2645,23 +2645,39 @@
           <t>14868</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>18564</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>3696</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/deepajewellersltd/DJL</t>
+          <t>https://www.moneycontrol.com/ipo/diamondjewellery/deepajewellers/DJL</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-07 13:49:18</t>
+          <t>2026-09-10 13:38:50</t>
         </is>
       </c>
     </row>
@@ -2673,9 +2689,9 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2713,23 +2729,39 @@
           <t>14818</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>14818</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/raysbelief/RoB</t>
+          <t>https://www.moneycontrol.com/ipo/hospitalhealthcare-services/raysbelief/RoB</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-07 13:49:18</t>
+          <t>2026-09-10 13:38:50</t>
         </is>
       </c>
     </row>
@@ -2741,9 +2773,9 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2783,17 +2815,21 @@
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/pranavconstructionsltd/PCL02</t>
+          <t>https://www.moneycontrol.com/ipo/pranavconstructions/PCL02</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-07 13:49:18</t>
+          <t>2026-09-10 13:38:50</t>
         </is>
       </c>
     </row>
@@ -2805,9 +2841,9 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2837,7 +2873,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>172-182</t>
+          <t>182</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2847,17 +2883,21 @@
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/glasswallsystemsindialtd/GWSIL</t>
+          <t>https://www.moneycontrol.com/ipo/glasswallsystemsindia/GWSIL</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-07 13:49:18</t>
+          <t>2026-09-10 13:38:50</t>
         </is>
       </c>
     </row>
@@ -2869,9 +2909,9 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2901,7 +2941,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>601-632</t>
+          <t>632</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2911,17 +2951,21 @@
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kanoharelectricalsltd/KEL09</t>
+          <t>https://www.moneycontrol.com/ipo/kanoharelectricals/KEL09</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-07 13:49:18</t>
+          <t>2026-09-10 13:38:50</t>
         </is>
       </c>
     </row>
@@ -2933,9 +2977,9 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2965,7 +3009,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>643-676</t>
+          <t>676</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2975,17 +3019,21 @@
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/prasolchemicalsltd/PCL03</t>
+          <t>https://www.moneycontrol.com/ipo/prasolchemicals/PCL03</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-07 13:49:18</t>
+          <t>2026-09-10 13:38:50</t>
         </is>
       </c>
     </row>
@@ -2997,9 +3045,9 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3029,7 +3077,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>132-139</t>
+          <t>139</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3039,17 +3087,21 @@
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/assetreconstructioncompanyindialtd/ARCIL</t>
+          <t>https://www.moneycontrol.com/ipo/assetreconstructioncompanyindia/ARCIL</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-07 13:49:18</t>
+          <t>2026-09-10 13:38:50</t>
         </is>
       </c>
     </row>
@@ -3061,9 +3113,9 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3093,7 +3145,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>241-254</t>
+          <t>254</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3103,17 +3155,21 @@
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/karamtaraengineeringltd/K05</t>
+          <t>https://www.moneycontrol.com/ipo/karamtaraengineering/K05</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-07 13:49:18</t>
+          <t>2026-09-10 13:38:50</t>
         </is>
       </c>
     </row>
@@ -3125,9 +3181,9 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3157,7 +3213,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>139-146</t>
+          <t>146</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3167,17 +3223,21 @@
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/lccprojectsltd/LPL02</t>
+          <t>https://www.moneycontrol.com/ipo/lccprojects/LPL02</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-07 13:49:18</t>
+          <t>2026-09-10 13:38:50</t>
         </is>
       </c>
     </row>
@@ -3189,9 +3249,9 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3221,7 +3281,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>322-339</t>
+          <t>339</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3231,17 +3291,21 @@
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/manipalpaymentidentitysolutionsltd/MPISL</t>
+          <t>https://www.moneycontrol.com/ipo/manipalpaymentidentitysolutions/MPISL</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-07 13:49:18</t>
+          <t>2026-09-10 13:38:50</t>
         </is>
       </c>
     </row>
@@ -3253,9 +3317,9 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3285,7 +3349,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>384-404</t>
+          <t>404</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3295,126 +3359,138 @@
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/rentomojoltd/RL10</t>
+          <t>https://www.moneycontrol.com/ipo/rentomojo/RL10</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-07 13:49:18</t>
+          <t>2026-09-10 13:38:50</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Veegaland Developers Ltd</t>
+          <t>Steamhouse India</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sep 10, 2026</t>
+          <t>Sep 09, 2026</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>Sep 11, 2026</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>Sep 15, 2026</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Sep 16, 2026</t>
-        </is>
-      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>185</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>130-140</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>14980</t>
+          <t>14985</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/veegalanddevelopersltd/VDL02</t>
+          <t>https://www.moneycontrol.com/ipo/steamhouseindia/SIL35</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-07 13:49:18</t>
+          <t>2026-09-10 13:38:50</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Veegaland Developers Ltd</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 10, 2026</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 15, 2026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Sep 16, 2026</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>107</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>140</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -3424,19 +3500,19 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/veegalanddevelopers/VDL02</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-10 13:38:50</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Manika Plastech</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -3448,33 +3524,37 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Sep 11, 2026</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 16, 2026</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sep 21, 2026</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>348</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>40-43</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>14964</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -3484,19 +3564,19 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/manikaplastech/MPL06</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-09-10 13:38:50</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Jindal Supreme India Ltd</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -3508,33 +3588,37 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 16, 2026</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 18, 2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Sep 21, 2026</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sep 23, 2026</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>161</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>88-93</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>14973</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -3544,19 +3628,19 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/jindalsupremeindialtd/JSI01</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-09-10 13:38:50</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -3568,17 +3652,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -3589,12 +3673,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -3604,19 +3688,19 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -3628,33 +3712,33 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -3664,75 +3748,79 @@
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>118000</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -3744,28 +3832,28 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3780,19 +3868,19 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -3804,33 +3892,33 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>Sep 01, 2026</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
           <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3840,7 +3928,7 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -3852,65 +3940,241 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>125-132</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>132000</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:25:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Q&amp;T Foods Ltd</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Aug 17, 2026</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:24:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Shanti Inorganics Ltd</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aug 31, 2026</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Sep 02, 2026</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Sep 03, 2026</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>79-83</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>132800</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:29:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R47"/>
+  <autoFilter ref="A1:R50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R50"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-10 13:38:50</t>
+          <t>2026-09-10 23:59:07</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-10 13:38:50</t>
+          <t>2026-09-10 23:59:07</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-10 13:38:50</t>
+          <t>2026-09-10 23:59:07</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-10 13:38:50</t>
+          <t>2026-09-10 23:59:07</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-10 13:38:50</t>
+          <t>2026-09-10 23:59:07</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-10 13:38:50</t>
+          <t>2026-09-10 23:59:07</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-10 13:38:50</t>
+          <t>2026-09-10 23:59:07</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-10 13:38:50</t>
+          <t>2026-09-10 23:59:07</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-10 13:38:50</t>
+          <t>2026-09-10 23:59:07</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-10 13:38:50</t>
+          <t>2026-09-10 23:59:07</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-10 13:38:50</t>
+          <t>2026-09-10 23:59:07</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3429,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-10 13:38:50</t>
+          <t>2026-09-10 23:59:07</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,11 @@
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
@@ -3505,7 +3509,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-10 13:38:50</t>
+          <t>2026-09-10 23:59:07</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3573,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-10 13:38:50</t>
+          <t>2026-09-10 23:59:07</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3637,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-10 13:38:50</t>
+          <t>2026-09-10 23:59:07</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3824,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Hero Motors Ltd</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -3832,35 +3836,27 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 16, 2026</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 18, 2026</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>138000</t>
-        </is>
-      </c>
+          <t>79-84</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -3868,19 +3864,19 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/heromotorsltd/HML02</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-09-10 23:59:07</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Kheria Autocomp Ltd</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -3892,35 +3888,27 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>46-48</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>144000</t>
-        </is>
-      </c>
+          <t>96-101</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -3928,75 +3916,79 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-10 23:59:07</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -4008,33 +4000,33 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -4044,26 +4036,26 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4082,41 +4074,37 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>79-83</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>132800</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -4128,33 +4116,33 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>Aug 14, 2026</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -4164,17 +4152,293 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:24:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SS Retail Ltd</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Sep 16, 2026</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Sep 21, 2026</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>403-424</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/ssretailltd/SRL03</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>2026-09-10 23:59:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Shanti Inorganics Ltd</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aug 31, 2026</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Sep 02, 2026</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Sep 03, 2026</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>79-83</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>132800</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:29:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Sonaselection India Ltd</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Sep 21, 2026</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Sep 22, 2026</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>94-99</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/sonaselectionindialtd/SIL36</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2026-09-10 23:59:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab Ltd</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>324-341</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/vamawovenfabltd/VWL01</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2026-09-10 23:59:07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R50"/>
+  <autoFilter ref="A1:R55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -2677,7 +2677,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
@@ -2841,9 +2841,9 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2885,7 +2885,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>82</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
@@ -2909,9 +2909,9 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2953,7 +2953,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
@@ -2977,9 +2977,9 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3021,7 +3021,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3429,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
@@ -3521,9 +3521,9 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>40-43</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3573,14 +3573,14 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jindal Supreme India Ltd</t>
+          <t>Hero Motors Ltd</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -3612,17 +3612,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>178</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>88-93</t>
+          <t>79-84</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>14973</t>
+          <t>14952</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -3632,19 +3632,19 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/jindalsupremeindialtd/JSI01</t>
+          <t>https://www.moneycontrol.com/ipo/heromotorsltd/HML02</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Jindal Supreme India Ltd</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -3656,33 +3656,37 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 16, 2026</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 18, 2026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Sep 21, 2026</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sep 23, 2026</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>161</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>88-93</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>14973</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -3692,19 +3696,19 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/jindalsupremeindialtd/JSI01</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>SS Retail Ltd</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -3716,33 +3720,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Sep 16, 2026</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 18, 2026</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Sep 21, 2026</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sep 23, 2026</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>403-424</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -3752,19 +3760,19 @@
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/ssretailltd/SRL03</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Sonaselection India Ltd</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -3776,33 +3784,37 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Sep 22, 2026</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sep 24, 2026</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>94-99</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>14850</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -3812,19 +3824,19 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/sonaselectionindialtd/SIL36</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hero Motors Ltd</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -3836,27 +3848,35 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sep 16, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>79-84</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>128-135</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>135000</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -3864,19 +3884,19 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/heromotorsltd/HML02</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kheria Autocomp Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -3888,27 +3908,35 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sep 22, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96-101</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>179-189</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>113400</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -3916,19 +3944,19 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -3940,33 +3968,33 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3976,19 +4004,19 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Kheria Autocomp Ltd</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -4000,35 +4028,27 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>46-48</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>144000</t>
-        </is>
-      </c>
+          <t>96-101</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -4036,75 +4056,79 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -4116,33 +4140,33 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -4152,71 +4176,75 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SS Retail Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sep 16, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>403-424</t>
+          <t>575</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/ssretailltd/SRL03</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -4228,33 +4256,33 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -4264,19 +4292,19 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sonaselection India Ltd</t>
+          <t>Shanti Inorganics Ltd</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -4288,27 +4316,35 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sep 22, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>94-99</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>79-83</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>132800</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -4316,12 +4352,12 @@
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/sonaselectionindialtd/SIL36</t>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4469,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-10 23:59:07</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R55"/>
+  <dimension ref="A1:R56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-12 13:25:46</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-12 13:25:46</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-12 13:25:46</t>
         </is>
       </c>
     </row>
@@ -3045,9 +3045,9 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3089,7 +3089,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-12 13:25:46</t>
         </is>
       </c>
     </row>
@@ -3113,9 +3113,9 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3157,7 +3157,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>63</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-12 13:25:46</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-12 13:25:46</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,11 @@
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
@@ -3573,7 +3577,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-12 13:25:46</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3641,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-12 13:25:46</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3705,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-12 13:25:46</t>
         </is>
       </c>
     </row>
@@ -3765,14 +3769,14 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-12 13:25:46</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sonaselection India Ltd</t>
+          <t>National Stock Exchange of India</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -3804,17 +3808,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>94-99</t>
+          <t>1700-1785</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>14850</t>
+          <t>14280</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -3824,19 +3828,19 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/sonaselectionindialtd/SIL36</t>
+          <t>https://www.moneycontrol.com/ipo/nationalstockexchangeindia/NSEoIL</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-12 13:25:46</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Sonaselection India Ltd</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -3848,33 +3852,37 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Sep 22, 2026</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sep 24, 2026</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>94-99</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>14850</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -3884,19 +3892,19 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/sonaselectionindialtd/SIL36</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-12 13:25:46</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -3908,33 +3916,33 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3944,19 +3952,19 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -3968,33 +3976,33 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -4004,19 +4012,19 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kheria Autocomp Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -4028,27 +4036,35 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sep 22, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96-101</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>118000</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -4056,19 +4072,19 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Kheria Autocomp Ltd</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -4080,33 +4096,33 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>96-101</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -4116,19 +4132,19 @@
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -4140,33 +4156,33 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -4176,135 +4192,135 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>Sep 01, 2026</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
           <t>Sep 02, 2026</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Sep 03, 2026</t>
-        </is>
-      </c>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>46-48</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>144000</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>138000</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -4316,33 +4332,33 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -4352,19 +4368,19 @@
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Shanti Inorganics Ltd</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -4376,33 +4392,33 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>79-83</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>132800</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -4412,19 +4428,19 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Vama Wovenfab Ltd</t>
+          <t>Technocrats Plasma Systems Ltd</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -4436,27 +4452,35 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sep 15, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>324-341</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -4464,17 +4488,77 @@
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2026-08-11 21:41:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab Ltd</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>324-341</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>136400</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/vamawovenfabltd/VWL01</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R55"/>
+  <autoFilter ref="A1:R56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -2677,7 +2677,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-12 13:25:46</t>
+          <t>2026-09-12 23:14:55</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-12 13:25:46</t>
+          <t>2026-09-12 23:14:55</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-12 13:25:46</t>
+          <t>2026-09-12 23:14:55</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-12 13:25:46</t>
+          <t>2026-09-12 23:14:55</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-12 13:25:46</t>
+          <t>2026-09-12 23:14:55</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-12 13:25:46</t>
+          <t>2026-09-12 23:14:55</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-12 13:25:46</t>
+          <t>2026-09-12 23:14:55</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-12 13:25:46</t>
+          <t>2026-09-12 23:14:55</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-12 13:25:46</t>
+          <t>2026-09-12 23:14:55</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-12 13:25:46</t>
+          <t>2026-09-12 23:14:55</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-12 13:25:46</t>
+          <t>2026-09-12 23:14:55</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-12 13:25:46</t>
+          <t>2026-09-12 23:14:55</t>
         </is>
       </c>
     </row>
